--- a/test_data/upper_body.xlsx
+++ b/test_data/upper_body.xlsx
@@ -84,8 +84,8 @@
     <sheet name="set_joint_min_angle" sheetId="76" state="visible" r:id="rId76"/>
     <sheet name="set_joint_max_angle" sheetId="77" state="visible" r:id="rId77"/>
     <sheet name="send_upper_angle" sheetId="78" state="visible" r:id="rId78"/>
-    <sheet name="upper_jog_angle" sheetId="79" state="visible" r:id="rId79"/>
-    <sheet name="upper_jog_angle_increment" sheetId="80" state="visible" r:id="rId80"/>
+    <sheet name="upper_jog_angle_increment" sheetId="79" state="visible" r:id="rId79"/>
+    <sheet name="upper_jog_angle" sheetId="80" state="visible" r:id="rId80"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'get_upper_main_version'!$A$1:$F$2</definedName>
@@ -36685,7 +36685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K59"/>
+  <dimension ref="A1:K74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36716,7 +36716,7 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>direction</t>
+          <t>increment</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
@@ -36726,7 +36726,7 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>target_limit</t>
+          <t>range_limit</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
@@ -36751,12 +36751,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>左臂J1以速度10执行负向Jog运动到软件限位-150度</t>
+          <t>左臂J1以速度10步进30度后回零</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>upper_jog_angle</t>
+          <t>upper_jog_angle_increment</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -36768,20 +36768,17 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G2" t="n">
         <v>10</v>
       </c>
-      <c r="H2" t="n">
-        <v>-150</v>
-      </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
@@ -36791,12 +36788,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>左臂J1以速度20执行正向Jog运动到软件限位176度</t>
+          <t>左臂J2以速度10步进30度后回零</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>upper_jog_angle</t>
+          <t>upper_jog_angle_increment</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -36805,23 +36802,20 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="G3" t="n">
         <v>20</v>
       </c>
-      <c r="H3" t="n">
-        <v>176</v>
-      </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
@@ -36831,12 +36825,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>左臂J2以速度30执行负向Jog运动到软件限位-72度</t>
+          <t>左臂J3以速度10步进30度后回零</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>upper_jog_angle</t>
+          <t>upper_jog_angle_increment</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -36845,23 +36839,20 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G4" t="n">
         <v>30</v>
       </c>
-      <c r="H4" t="n">
-        <v>-72</v>
-      </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
@@ -36871,12 +36862,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>左臂J2以速度40执行正向Jog运动到软件限位125度</t>
+          <t>左臂J4以速度10步进-30度后回零</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>upper_jog_angle</t>
+          <t>upper_jog_angle_increment</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -36885,23 +36876,20 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>-30</v>
       </c>
       <c r="G5" t="n">
         <v>40</v>
       </c>
-      <c r="H5" t="n">
-        <v>125</v>
-      </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
@@ -36911,12 +36899,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>左臂J3以速度50执行负向Jog运动到软件限位-163度</t>
+          <t>左臂J5以速度10步进30度后回零</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>upper_jog_angle</t>
+          <t>upper_jog_angle_increment</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -36925,23 +36913,20 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G6" t="n">
         <v>50</v>
       </c>
-      <c r="H6" t="n">
-        <v>-163</v>
-      </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
@@ -36951,12 +36936,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>左臂J3以速度20执行正向Jog运动到软件限位167度</t>
+          <t>左臂J6以速度10步进30度后回零</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>upper_jog_angle</t>
+          <t>upper_jog_angle_increment</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -36965,23 +36950,20 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="G7" t="n">
         <v>20</v>
       </c>
-      <c r="H7" t="n">
-        <v>167</v>
-      </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
@@ -36991,12 +36973,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>左臂J4以速度40执行负向Jog运动到软件限位-149度</t>
+          <t>左臂J7以速度10步进30度后回零</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>upper_jog_angle</t>
+          <t>upper_jog_angle_increment</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -37005,23 +36987,20 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G8" t="n">
         <v>40</v>
       </c>
-      <c r="H8" t="n">
-        <v>-149</v>
-      </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
@@ -37031,37 +37010,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>左臂J4以速度70执行正向Jog运动到软件限位1度</t>
+          <t>右臂J1以速度10步进30度后回零</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>upper_jog_angle</t>
+          <t>upper_jog_angle_increment</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="G9" t="n">
         <v>70</v>
       </c>
-      <c r="H9" t="n">
-        <v>1</v>
-      </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
@@ -37071,37 +37047,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>左臂J5以速度80执行负向Jog运动到软件限位-179度</t>
+          <t>右臂J2以速度10步进30度后回零</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>upper_jog_angle</t>
+          <t>upper_jog_angle_increment</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G10" t="n">
         <v>80</v>
       </c>
-      <c r="H10" t="n">
-        <v>-179</v>
-      </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
@@ -37111,37 +37084,34 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>左臂J5以速度20执行正向Jog运动到软件限位148度</t>
+          <t>右臂J3以速度10步进30度后回零</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>upper_jog_angle</t>
+          <t>upper_jog_angle_increment</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="G11" t="n">
         <v>20</v>
       </c>
-      <c r="H11" t="n">
-        <v>148</v>
-      </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
@@ -37151,37 +37121,34 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>左臂J6以速度90执行负向Jog运动到软件限位-87度</t>
+          <t>右臂J4以速度10步进-30度后回零</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>upper_jog_angle</t>
+          <t>upper_jog_angle_increment</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
       <c r="G12" t="n">
         <v>90</v>
       </c>
-      <c r="H12" t="n">
-        <v>-87</v>
-      </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
@@ -37191,37 +37158,34 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>左臂J6以速度100执行正向Jog运动到软件限位42度</t>
+          <t>右臂J5以速度10步进30度后回零</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>upper_jog_angle</t>
+          <t>upper_jog_angle_increment</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="G13" t="n">
         <v>100</v>
       </c>
-      <c r="H13" t="n">
-        <v>42</v>
-      </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
@@ -37231,37 +37195,34 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>左臂J7以速度50执行负向Jog运动到软件限位-80度</t>
+          <t>右臂J6以速度10步进30度后回零</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>upper_jog_angle</t>
+          <t>upper_jog_angle_increment</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G14" t="n">
         <v>50</v>
       </c>
-      <c r="H14" t="n">
-        <v>-80</v>
-      </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
@@ -37271,37 +37232,34 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>左臂J7以速度60执行正向Jog运动到软件限位92度</t>
+          <t>右臂J7以速度10步进30度后回零</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>upper_jog_angle</t>
+          <t>upper_jog_angle_increment</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="E15" t="n">
         <v>7</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
       </c>
-      <c r="H15" t="n">
-        <v>92</v>
-      </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
@@ -37311,37 +37269,34 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>右臂J1以速度70执行负向Jog运动到软件限位-150度</t>
+          <t>双臂J1以速度10步进30度后回零</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>upper_jog_angle</t>
+          <t>upper_jog_angle_increment</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>both</t>
         </is>
       </c>
       <c r="E16" t="n">
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G16" t="n">
         <v>70</v>
       </c>
-      <c r="H16" t="n">
-        <v>-150</v>
-      </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
@@ -37351,37 +37306,34 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>右臂J1以速度80执行正向Jog运动到软件限位176度</t>
+          <t>双臂J2以速度10步进30度后回零</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>upper_jog_angle</t>
+          <t>upper_jog_angle_increment</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>both</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="G17" t="n">
         <v>80</v>
       </c>
-      <c r="H17" t="n">
-        <v>176</v>
-      </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
@@ -37391,37 +37343,34 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>右臂J2以速度10执行负向Jog运动到软件限位-72度</t>
+          <t>双臂J3以速度10步进30度后回零</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>upper_jog_angle</t>
+          <t>upper_jog_angle_increment</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>both</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G18" t="n">
         <v>10</v>
       </c>
-      <c r="H18" t="n">
-        <v>-72</v>
-      </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
@@ -37431,37 +37380,34 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>右臂J2以速度20执行正向Jog运动到软件限位125度</t>
+          <t>双臂J4以速度10步进-30度后回零</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>upper_jog_angle</t>
+          <t>upper_jog_angle_increment</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>both</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>-30</v>
       </c>
       <c r="G19" t="n">
         <v>20</v>
       </c>
-      <c r="H19" t="n">
-        <v>125</v>
-      </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
@@ -37471,37 +37417,34 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>右臂J3以速度1执行负向Jog运动到软件限位-163度</t>
+          <t>双臂J5以速度10步进30度后回零</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>upper_jog_angle</t>
+          <t>upper_jog_angle_increment</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>both</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
       </c>
-      <c r="H20" t="n">
-        <v>-163</v>
-      </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
@@ -37511,37 +37454,34 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>右臂J3以速度20执行正向Jog运动到软件限位167度</t>
+          <t>双臂J6以速度10步进30度后回零</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>upper_jog_angle</t>
+          <t>upper_jog_angle_increment</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>both</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
-      <c r="H21" t="n">
-        <v>167</v>
-      </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
@@ -37551,37 +37491,34 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>右臂J4以速度50执行负向Jog运动到软件限位-149度</t>
+          <t>双臂J7以速度10步进30度后回零</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>upper_jog_angle</t>
+          <t>upper_jog_angle_increment</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>both</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G22" t="n">
         <v>50</v>
       </c>
-      <c r="H22" t="n">
-        <v>-149</v>
-      </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
@@ -37591,37 +37528,34 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>右臂J4以速度60执行正向Jog运动到软件限位1度</t>
+          <t>左臂J1步进-327度，验证超限完整行程326度</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>upper_jog_angle</t>
+          <t>upper_jog_angle_increment</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>-327</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1</v>
+        <v>326</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>range_exception</t>
         </is>
       </c>
     </row>
@@ -37631,37 +37565,34 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>右臂J5以速度80执行负向Jog运动到软件限位-179度</t>
+          <t>左臂J1步进327度，验证超限完整行程326度</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>upper_jog_angle</t>
+          <t>upper_jog_angle_increment</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>327</v>
       </c>
       <c r="G24" t="n">
         <v>80</v>
       </c>
       <c r="H24" t="n">
-        <v>-179</v>
-      </c>
-      <c r="I24" t="n">
-        <v>1</v>
+        <v>326</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>range_exception</t>
         </is>
       </c>
     </row>
@@ -37671,37 +37602,34 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>右臂J5以速度40执行正向Jog运动到软件限位148度</t>
+          <t>左臂J2步进-198度，验证超限完整行程197度</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>upper_jog_angle</t>
+          <t>upper_jog_angle_increment</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>-198</v>
       </c>
       <c r="G25" t="n">
         <v>40</v>
       </c>
       <c r="H25" t="n">
-        <v>148</v>
-      </c>
-      <c r="I25" t="n">
-        <v>1</v>
+        <v>197</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>range_exception</t>
         </is>
       </c>
     </row>
@@ -37711,37 +37639,34 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>右臂J6以速度30执行负向Jog运动到软件限位-87度</t>
+          <t>左臂J2步进198度，验证超限完整行程197度</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>upper_jog_angle</t>
+          <t>upper_jog_angle_increment</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>198</v>
       </c>
       <c r="G26" t="n">
         <v>30</v>
       </c>
       <c r="H26" t="n">
-        <v>-87</v>
-      </c>
-      <c r="I26" t="n">
-        <v>1</v>
+        <v>197</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>range_exception</t>
         </is>
       </c>
     </row>
@@ -37751,37 +37676,34 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>右臂J6以速度20执行正向Jog运动到软件限位42度</t>
+          <t>左臂J3步进-331度，验证超限完整行程330度</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>upper_jog_angle</t>
+          <t>upper_jog_angle_increment</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>-331</v>
       </c>
       <c r="G27" t="n">
         <v>20</v>
       </c>
       <c r="H27" t="n">
-        <v>42</v>
-      </c>
-      <c r="I27" t="n">
-        <v>1</v>
+        <v>330</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>range_exception</t>
         </is>
       </c>
     </row>
@@ -37791,37 +37713,34 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>右臂J7以速度10执行负向Jog运动到软件限位-80度</t>
+          <t>左臂J3步进331度，验证超限完整行程330度</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>upper_jog_angle</t>
+          <t>upper_jog_angle_increment</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>331</v>
       </c>
       <c r="G28" t="n">
         <v>10</v>
       </c>
       <c r="H28" t="n">
-        <v>-80</v>
-      </c>
-      <c r="I28" t="n">
-        <v>1</v>
+        <v>330</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>range_exception</t>
         </is>
       </c>
     </row>
@@ -37831,37 +37750,34 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>右臂J7以速度26执行正向Jog运动到软件限位92度</t>
+          <t>左臂J4步进-151度，验证超限完整行程150度</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>upper_jog_angle</t>
+          <t>upper_jog_angle_increment</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>-151</v>
       </c>
       <c r="G29" t="n">
         <v>26</v>
       </c>
       <c r="H29" t="n">
-        <v>92</v>
-      </c>
-      <c r="I29" t="n">
-        <v>1</v>
+        <v>150</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>range_exception</t>
         </is>
       </c>
     </row>
@@ -37871,37 +37787,34 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>双臂J1以速度35执行负向Jog运动到软件限位-150度</t>
+          <t>左臂J4步进151度，验证超限完整行程150度</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>upper_jog_angle</t>
+          <t>upper_jog_angle_increment</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>left</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="G30" t="n">
         <v>35</v>
       </c>
       <c r="H30" t="n">
-        <v>-150</v>
-      </c>
-      <c r="I30" t="n">
-        <v>1</v>
+        <v>150</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>range_exception</t>
         </is>
       </c>
     </row>
@@ -37911,37 +37824,34 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>双臂J1以速度41执行正向Jog运动到软件限位176度</t>
+          <t>左臂J5步进-328度，验证超限完整行程327度</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>upper_jog_angle</t>
+          <t>upper_jog_angle_increment</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>left</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>-328</v>
       </c>
       <c r="G31" t="n">
         <v>41</v>
       </c>
       <c r="H31" t="n">
-        <v>176</v>
-      </c>
-      <c r="I31" t="n">
-        <v>1</v>
+        <v>327</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>range_exception</t>
         </is>
       </c>
     </row>
@@ -37951,37 +37861,34 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>双臂J2以速度10执行负向Jog运动到软件限位-72度</t>
+          <t>左臂J5步进328度，验证超限完整行程327度</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>upper_jog_angle</t>
+          <t>upper_jog_angle_increment</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>left</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>328</v>
       </c>
       <c r="G32" t="n">
         <v>10</v>
       </c>
       <c r="H32" t="n">
-        <v>-72</v>
-      </c>
-      <c r="I32" t="n">
-        <v>1</v>
+        <v>327</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>range_exception</t>
         </is>
       </c>
     </row>
@@ -37991,37 +37898,34 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>双臂J2以速度20执行正向Jog运动到软件限位125度</t>
+          <t>左臂J6步进-130度，验证超限完整行程129度</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>upper_jog_angle</t>
+          <t>upper_jog_angle_increment</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>left</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F33" t="n">
-        <v>1</v>
+        <v>-130</v>
       </c>
       <c r="G33" t="n">
         <v>20</v>
       </c>
       <c r="H33" t="n">
-        <v>125</v>
-      </c>
-      <c r="I33" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>range_exception</t>
         </is>
       </c>
     </row>
@@ -38031,37 +37935,34 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>双臂J3以速度50执行负向Jog运动到软件限位-163度</t>
+          <t>左臂J6步进130度，验证超限完整行程129度</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>upper_jog_angle</t>
+          <t>upper_jog_angle_increment</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>left</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="G34" t="n">
         <v>50</v>
       </c>
       <c r="H34" t="n">
-        <v>-163</v>
-      </c>
-      <c r="I34" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>range_exception</t>
         </is>
       </c>
     </row>
@@ -38071,37 +37972,34 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>双臂J3以速度60执行正向Jog运动到软件限位167度</t>
+          <t>左臂J7步进-173度，验证超限完整行程172度</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>upper_jog_angle</t>
+          <t>upper_jog_angle_increment</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>left</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F35" t="n">
-        <v>1</v>
+        <v>-173</v>
       </c>
       <c r="G35" t="n">
         <v>60</v>
       </c>
       <c r="H35" t="n">
-        <v>167</v>
-      </c>
-      <c r="I35" t="n">
-        <v>1</v>
+        <v>172</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>range_exception</t>
         </is>
       </c>
     </row>
@@ -38111,37 +38009,34 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>双臂J4以速度80执行负向Jog运动到软件限位-149度</t>
+          <t>左臂J7步进173度，验证超限完整行程172度</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>upper_jog_angle</t>
+          <t>upper_jog_angle_increment</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>left</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>173</v>
       </c>
       <c r="G36" t="n">
         <v>80</v>
       </c>
       <c r="H36" t="n">
-        <v>-149</v>
-      </c>
-      <c r="I36" t="n">
-        <v>1</v>
+        <v>172</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>range_exception</t>
         </is>
       </c>
     </row>
@@ -38151,37 +38046,34 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>双臂J4以速度40执行正向Jog运动到软件限位1度</t>
+          <t>右臂J1步进-327度，验证超限完整行程326度</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>upper_jog_angle</t>
+          <t>upper_jog_angle_increment</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>right</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F37" t="n">
-        <v>1</v>
+        <v>-327</v>
       </c>
       <c r="G37" t="n">
         <v>40</v>
       </c>
       <c r="H37" t="n">
-        <v>1</v>
-      </c>
-      <c r="I37" t="n">
-        <v>1</v>
+        <v>326</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>range_exception</t>
         </is>
       </c>
     </row>
@@ -38191,37 +38083,34 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>双臂J5以速度30执行负向Jog运动到软件限位-179度</t>
+          <t>右臂J1步进327度，验证超限完整行程326度</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>upper_jog_angle</t>
+          <t>upper_jog_angle_increment</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>right</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>327</v>
       </c>
       <c r="G38" t="n">
         <v>30</v>
       </c>
       <c r="H38" t="n">
-        <v>-179</v>
-      </c>
-      <c r="I38" t="n">
-        <v>1</v>
+        <v>326</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>range_exception</t>
         </is>
       </c>
     </row>
@@ -38231,37 +38120,34 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>双臂J5以速度20执行正向Jog运动到软件限位148度</t>
+          <t>右臂J2步进-198度，验证超限完整行程197度</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>upper_jog_angle</t>
+          <t>upper_jog_angle_increment</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>right</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F39" t="n">
-        <v>1</v>
+        <v>-198</v>
       </c>
       <c r="G39" t="n">
         <v>20</v>
       </c>
       <c r="H39" t="n">
-        <v>148</v>
-      </c>
-      <c r="I39" t="n">
-        <v>1</v>
+        <v>197</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>range_exception</t>
         </is>
       </c>
     </row>
@@ -38271,37 +38157,34 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>双臂J6以速度10执行负向Jog运动到软件限位-87度</t>
+          <t>右臂J2步进198度，验证超限完整行程197度</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>upper_jog_angle</t>
+          <t>upper_jog_angle_increment</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>right</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>198</v>
       </c>
       <c r="G40" t="n">
         <v>10</v>
       </c>
       <c r="H40" t="n">
-        <v>-87</v>
-      </c>
-      <c r="I40" t="n">
-        <v>1</v>
+        <v>197</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>range_exception</t>
         </is>
       </c>
     </row>
@@ -38311,37 +38194,34 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>双臂J6以速度26执行正向Jog运动到软件限位42度</t>
+          <t>右臂J3步进-331度，验证超限完整行程330度</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>upper_jog_angle</t>
+          <t>upper_jog_angle_increment</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>right</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F41" t="n">
-        <v>1</v>
+        <v>-331</v>
       </c>
       <c r="G41" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="H41" t="n">
-        <v>42</v>
-      </c>
-      <c r="I41" t="n">
-        <v>1</v>
+        <v>330</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>range_exception</t>
         </is>
       </c>
     </row>
@@ -38351,37 +38231,34 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>双臂J7以速度35执行负向Jog运动到软件限位-80度</t>
+          <t>右臂J3步进331度，验证超限完整行程330度</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>upper_jog_angle</t>
+          <t>upper_jog_angle_increment</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>right</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>331</v>
       </c>
       <c r="G42" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="H42" t="n">
-        <v>-80</v>
-      </c>
-      <c r="I42" t="n">
-        <v>1</v>
+        <v>330</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>range_exception</t>
         </is>
       </c>
     </row>
@@ -38391,37 +38268,34 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>双臂J7以速度41执行正向Jog运动到软件限位92度</t>
+          <t>右臂J4步进-151度，验证超限完整行程150度</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>upper_jog_angle</t>
+          <t>upper_jog_angle_increment</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>right</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F43" t="n">
-        <v>1</v>
+        <v>-151</v>
       </c>
       <c r="G43" t="n">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="H43" t="n">
-        <v>92</v>
-      </c>
-      <c r="I43" t="n">
-        <v>1</v>
+        <v>150</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>range_exception</t>
         </is>
       </c>
     </row>
@@ -38431,36 +38305,34 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>左臂刷新模式下调用J1正向Jog运动，验证返回失败并提示切换插补模式</t>
+          <t>右臂J4步进151度，验证超限完整行程150度</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>upper_jog_angle</t>
+          <t>upper_jog_angle_increment</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F44" t="n">
-        <v>1</v>
+        <v>151</v>
       </c>
       <c r="G44" t="n">
-        <v>10</v>
+        <v>80</v>
+      </c>
+      <c r="H44" t="n">
+        <v>150</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>unsupported</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>刷新模式无法使用JOG运动</t>
+          <t>range_exception</t>
         </is>
       </c>
     </row>
@@ -38470,31 +38342,34 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>左臂J7速度为0，验证速度超限</t>
+          <t>右臂J5步进-328度，验证超限完整行程327度</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>upper_jog_angle</t>
+          <t>upper_jog_angle_increment</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F45" t="n">
-        <v>1</v>
+        <v>-328</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>90</v>
+      </c>
+      <c r="H45" t="n">
+        <v>327</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>exception</t>
+          <t>range_exception</t>
         </is>
       </c>
     </row>
@@ -38504,31 +38379,34 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>左臂J7速度为101，验证速度超限</t>
+          <t>右臂J5步进328度，验证超限完整行程327度</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>upper_jog_angle</t>
+          <t>upper_jog_angle_increment</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F46" t="n">
-        <v>1</v>
+        <v>328</v>
       </c>
       <c r="G46" t="n">
-        <v>101</v>
+        <v>20</v>
+      </c>
+      <c r="H46" t="n">
+        <v>327</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>exception</t>
+          <t>range_exception</t>
         </is>
       </c>
     </row>
@@ -38538,31 +38416,34 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>左臂关节ID为0，验证关节ID超限</t>
+          <t>右臂J6步进-130度，验证超限完整行程129度</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>upper_jog_angle</t>
+          <t>upper_jog_angle_increment</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F47" t="n">
-        <v>1</v>
+        <v>-130</v>
       </c>
       <c r="G47" t="n">
-        <v>10</v>
+        <v>100</v>
+      </c>
+      <c r="H47" t="n">
+        <v>129</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>exception</t>
+          <t>range_exception</t>
         </is>
       </c>
     </row>
@@ -38572,31 +38453,34 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>左臂J7方向为-1，验证方向超限</t>
+          <t>右臂J6步进130度，验证超限完整行程129度</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>upper_jog_angle</t>
+          <t>upper_jog_angle_increment</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F48" t="n">
-        <v>-1</v>
+        <v>130</v>
       </c>
       <c r="G48" t="n">
-        <v>10</v>
+        <v>60</v>
+      </c>
+      <c r="H48" t="n">
+        <v>129</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>exception</t>
+          <t>range_exception</t>
         </is>
       </c>
     </row>
@@ -38606,31 +38490,34 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>左臂J7方向为2，验证方向超限</t>
+          <t>右臂J7步进-173度，验证超限完整行程172度</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>upper_jog_angle</t>
+          <t>upper_jog_angle_increment</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="E49" t="n">
         <v>7</v>
       </c>
       <c r="F49" t="n">
-        <v>2</v>
+        <v>-173</v>
       </c>
       <c r="G49" t="n">
-        <v>10</v>
+        <v>20</v>
+      </c>
+      <c r="H49" t="n">
+        <v>172</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>exception</t>
+          <t>range_exception</t>
         </is>
       </c>
     </row>
@@ -38640,12 +38527,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>右臂J7速度为0，验证速度超限</t>
+          <t>右臂J7步进173度，验证超限完整行程172度</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>upper_jog_angle</t>
+          <t>upper_jog_angle_increment</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -38657,14 +38544,17 @@
         <v>7</v>
       </c>
       <c r="F50" t="n">
-        <v>1</v>
+        <v>173</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>40</v>
+      </c>
+      <c r="H50" t="n">
+        <v>172</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>exception</t>
+          <t>range_exception</t>
         </is>
       </c>
     </row>
@@ -38674,31 +38564,34 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>右臂J7速度为101，验证速度超限</t>
+          <t>双臂J1步进-327度，验证超限完整行程326度</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>upper_jog_angle</t>
+          <t>upper_jog_angle_increment</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>both</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F51" t="n">
-        <v>1</v>
+        <v>-327</v>
       </c>
       <c r="G51" t="n">
-        <v>101</v>
+        <v>50</v>
+      </c>
+      <c r="H51" t="n">
+        <v>326</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>exception</t>
+          <t>range_exception</t>
         </is>
       </c>
     </row>
@@ -38708,31 +38601,34 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>右臂关节ID为0，验证关节ID超限</t>
+          <t>双臂J1步进327度，验证超限完整行程326度</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>upper_jog_angle</t>
+          <t>upper_jog_angle_increment</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>both</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" t="n">
-        <v>1</v>
+        <v>327</v>
       </c>
       <c r="G52" t="n">
-        <v>10</v>
+        <v>60</v>
+      </c>
+      <c r="H52" t="n">
+        <v>326</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>exception</t>
+          <t>range_exception</t>
         </is>
       </c>
     </row>
@@ -38742,31 +38638,34 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>右臂J7方向为-1，验证方向超限</t>
+          <t>双臂J2步进-198度，验证超限完整行程197度</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>upper_jog_angle</t>
+          <t>upper_jog_angle_increment</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>both</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F53" t="n">
-        <v>-1</v>
+        <v>-198</v>
       </c>
       <c r="G53" t="n">
-        <v>10</v>
+        <v>70</v>
+      </c>
+      <c r="H53" t="n">
+        <v>197</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>exception</t>
+          <t>range_exception</t>
         </is>
       </c>
     </row>
@@ -38776,31 +38675,34 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>右臂J7方向为2，验证方向超限</t>
+          <t>双臂J2步进198度，验证超限完整行程197度</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>upper_jog_angle</t>
+          <t>upper_jog_angle_increment</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>both</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F54" t="n">
-        <v>2</v>
+        <v>198</v>
       </c>
       <c r="G54" t="n">
-        <v>10</v>
+        <v>40</v>
+      </c>
+      <c r="H54" t="n">
+        <v>197</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>exception</t>
+          <t>range_exception</t>
         </is>
       </c>
     </row>
@@ -38810,12 +38712,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>双臂J7速度为0，验证速度超限</t>
+          <t>双臂J3步进-331度，验证超限完整行程330度</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>upper_jog_angle</t>
+          <t>upper_jog_angle_increment</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -38824,17 +38726,20 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F55" t="n">
-        <v>1</v>
+        <v>-331</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>60</v>
+      </c>
+      <c r="H55" t="n">
+        <v>330</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>exception</t>
+          <t>range_exception</t>
         </is>
       </c>
     </row>
@@ -38844,12 +38749,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>双臂J7速度为101，验证速度超限</t>
+          <t>双臂J3步进331度，验证超限完整行程330度</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>upper_jog_angle</t>
+          <t>upper_jog_angle_increment</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -38858,17 +38763,20 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F56" t="n">
-        <v>1</v>
+        <v>331</v>
       </c>
       <c r="G56" t="n">
-        <v>101</v>
+        <v>70</v>
+      </c>
+      <c r="H56" t="n">
+        <v>330</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>exception</t>
+          <t>range_exception</t>
         </is>
       </c>
     </row>
@@ -38878,12 +38786,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>双臂关节ID为0，验证关节ID超限</t>
+          <t>双臂J4步进-151度，验证超限完整行程150度</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>upper_jog_angle</t>
+          <t>upper_jog_angle_increment</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -38892,17 +38800,20 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F57" t="n">
-        <v>1</v>
+        <v>-151</v>
       </c>
       <c r="G57" t="n">
-        <v>10</v>
+        <v>80</v>
+      </c>
+      <c r="H57" t="n">
+        <v>150</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>exception</t>
+          <t>range_exception</t>
         </is>
       </c>
     </row>
@@ -38912,12 +38823,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>双臂J7方向为-1，验证方向超限</t>
+          <t>双臂J4步进151度，验证超限完整行程150度</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>upper_jog_angle</t>
+          <t>upper_jog_angle_increment</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -38926,17 +38837,20 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F58" t="n">
-        <v>-1</v>
+        <v>151</v>
       </c>
       <c r="G58" t="n">
-        <v>10</v>
+        <v>30</v>
+      </c>
+      <c r="H58" t="n">
+        <v>150</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>exception</t>
+          <t>range_exception</t>
         </is>
       </c>
     </row>
@@ -38946,12 +38860,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>双臂J7方向为2，验证方向超限</t>
+          <t>双臂J5步进-328度，验证超限完整行程327度</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>upper_jog_angle</t>
+          <t>upper_jog_angle_increment</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -38960,17 +38874,550 @@
         </is>
       </c>
       <c r="E59" t="n">
+        <v>5</v>
+      </c>
+      <c r="F59" t="n">
+        <v>-328</v>
+      </c>
+      <c r="G59" t="n">
+        <v>50</v>
+      </c>
+      <c r="H59" t="n">
+        <v>327</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>range_exception</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>双臂J5步进328度，验证超限完整行程327度</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>upper_jog_angle_increment</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>5</v>
+      </c>
+      <c r="F60" t="n">
+        <v>328</v>
+      </c>
+      <c r="G60" t="n">
+        <v>40</v>
+      </c>
+      <c r="H60" t="n">
+        <v>327</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>range_exception</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>双臂J6步进-130度，验证超限完整行程129度</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>upper_jog_angle_increment</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6</v>
+      </c>
+      <c r="F61" t="n">
+        <v>-130</v>
+      </c>
+      <c r="G61" t="n">
+        <v>20</v>
+      </c>
+      <c r="H61" t="n">
+        <v>129</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>range_exception</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>双臂J6步进130度，验证超限完整行程129度</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>upper_jog_angle_increment</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6</v>
+      </c>
+      <c r="F62" t="n">
+        <v>130</v>
+      </c>
+      <c r="G62" t="n">
+        <v>40</v>
+      </c>
+      <c r="H62" t="n">
+        <v>129</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>range_exception</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>双臂J7步进-173度，验证超限完整行程172度</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>upper_jog_angle_increment</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
         <v>7</v>
       </c>
-      <c r="F59" t="n">
-        <v>2</v>
-      </c>
-      <c r="G59" t="n">
+      <c r="F63" t="n">
+        <v>-173</v>
+      </c>
+      <c r="G63" t="n">
+        <v>80</v>
+      </c>
+      <c r="H63" t="n">
+        <v>172</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>range_exception</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>双臂J7步进173度，验证超限完整行程172度</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>upper_jog_angle_increment</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>7</v>
+      </c>
+      <c r="F64" t="n">
+        <v>173</v>
+      </c>
+      <c r="G64" t="n">
+        <v>20</v>
+      </c>
+      <c r="H64" t="n">
+        <v>172</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>range_exception</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>左臂J7速度为0，验证速度超限</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>upper_jog_angle_increment</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>7</v>
+      </c>
+      <c r="F65" t="n">
+        <v>30</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>exception</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>左臂J7速度为101，验证速度超限</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>upper_jog_angle_increment</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>7</v>
+      </c>
+      <c r="F66" t="n">
+        <v>30</v>
+      </c>
+      <c r="G66" t="n">
+        <v>101</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>exception</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>左臂关节ID为0，验证关节ID超限</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>upper_jog_angle_increment</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" t="n">
+        <v>30</v>
+      </c>
+      <c r="G67" t="n">
         <v>10</v>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t>exception</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>右臂J7速度为0，验证速度超限</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>upper_jog_angle_increment</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>7</v>
+      </c>
+      <c r="F68" t="n">
+        <v>30</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>exception</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>右臂J7速度为101，验证速度超限</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>upper_jog_angle_increment</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>7</v>
+      </c>
+      <c r="F69" t="n">
+        <v>30</v>
+      </c>
+      <c r="G69" t="n">
+        <v>101</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>exception</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>右臂关节ID为0，验证关节ID超限</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>upper_jog_angle_increment</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" t="n">
+        <v>30</v>
+      </c>
+      <c r="G70" t="n">
+        <v>10</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>exception</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>双臂J7速度为0，验证速度超限</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>upper_jog_angle_increment</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>7</v>
+      </c>
+      <c r="F71" t="n">
+        <v>30</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>exception</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>双臂J7速度为101，验证速度超限</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>upper_jog_angle_increment</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>7</v>
+      </c>
+      <c r="F72" t="n">
+        <v>30</v>
+      </c>
+      <c r="G72" t="n">
+        <v>101</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>exception</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>双臂关节ID为0，验证关节ID超限</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>upper_jog_angle_increment</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" t="n">
+        <v>30</v>
+      </c>
+      <c r="G73" t="n">
+        <v>10</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>exception</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>左臂刷新模式下调用J1正向步进30度，验证返回失败并提示切换插补模式</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>upper_jog_angle_increment</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" t="n">
+        <v>30</v>
+      </c>
+      <c r="G74" t="n">
+        <v>10</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>刷新模式无法使用JOG运动</t>
         </is>
       </c>
     </row>
@@ -39119,7 +39566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K74"/>
+  <dimension ref="A1:K58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39150,7 +39597,7 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>increment</t>
+          <t>direction</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
@@ -39160,7 +39607,7 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>range_limit</t>
+          <t>target_limit</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
@@ -39185,12 +39632,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>左臂J1以速度10步进30度后回零</t>
+          <t>左臂J1以速度10执行负向Jog运动到软件限位-150度</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>upper_jog_angle_increment</t>
+          <t>upper_jog_angle</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -39202,17 +39649,20 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>10</v>
       </c>
+      <c r="H2" t="n">
+        <v>-150</v>
+      </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>manual</t>
         </is>
       </c>
     </row>
@@ -39222,12 +39672,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>左臂J2以速度10步进30度后回零</t>
+          <t>左臂J1以速度20执行正向Jog运动到软件限位176度</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>upper_jog_angle_increment</t>
+          <t>upper_jog_angle</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -39236,20 +39686,23 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v>20</v>
       </c>
+      <c r="H3" t="n">
+        <v>176</v>
+      </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>manual</t>
         </is>
       </c>
     </row>
@@ -39259,12 +39712,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>左臂J3以速度10步进30度后回零</t>
+          <t>左臂J2以速度30执行负向Jog运动到软件限位-72度</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>upper_jog_angle_increment</t>
+          <t>upper_jog_angle</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -39273,20 +39726,23 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>30</v>
       </c>
+      <c r="H4" t="n">
+        <v>-72</v>
+      </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>manual</t>
         </is>
       </c>
     </row>
@@ -39296,12 +39752,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>左臂J4以速度10步进-30度后回零</t>
+          <t>左臂J2以速度40执行正向Jog运动到软件限位125度</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>upper_jog_angle_increment</t>
+          <t>upper_jog_angle</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -39310,20 +39766,23 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
         <v>40</v>
       </c>
+      <c r="H5" t="n">
+        <v>125</v>
+      </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>manual</t>
         </is>
       </c>
     </row>
@@ -39333,12 +39792,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>左臂J5以速度10步进30度后回零</t>
+          <t>左臂J3以速度50执行负向Jog运动到软件限位-163度</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>upper_jog_angle_increment</t>
+          <t>upper_jog_angle</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -39347,20 +39806,23 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>50</v>
       </c>
+      <c r="H6" t="n">
+        <v>-163</v>
+      </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>manual</t>
         </is>
       </c>
     </row>
@@ -39370,12 +39832,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>左臂J6以速度10步进30度后回零</t>
+          <t>左臂J3以速度20执行正向Jog运动到软件限位167度</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>upper_jog_angle_increment</t>
+          <t>upper_jog_angle</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -39384,20 +39846,23 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
         <v>20</v>
       </c>
+      <c r="H7" t="n">
+        <v>167</v>
+      </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>manual</t>
         </is>
       </c>
     </row>
@@ -39407,12 +39872,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>左臂J7以速度10步进30度后回零</t>
+          <t>左臂J4以速度40执行负向Jog运动到软件限位-149度</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>upper_jog_angle_increment</t>
+          <t>upper_jog_angle</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -39421,20 +39886,23 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F8" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
         <v>40</v>
       </c>
+      <c r="H8" t="n">
+        <v>-149</v>
+      </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>manual</t>
         </is>
       </c>
     </row>
@@ -39444,34 +39912,37 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>右臂J1以速度10步进30度后回零</t>
+          <t>左臂J4以速度70执行正向Jog运动到软件限位1度</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>upper_jog_angle_increment</t>
+          <t>upper_jog_angle</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F9" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
         <v>70</v>
       </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>manual</t>
         </is>
       </c>
     </row>
@@ -39481,34 +39952,37 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>右臂J2以速度10步进30度后回零</t>
+          <t>左臂J5以速度80执行负向Jog运动到软件限位-179度</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>upper_jog_angle_increment</t>
+          <t>upper_jog_angle</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F10" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
         <v>80</v>
       </c>
+      <c r="H10" t="n">
+        <v>-179</v>
+      </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>manual</t>
         </is>
       </c>
     </row>
@@ -39518,34 +39992,37 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>右臂J3以速度10步进30度后回零</t>
+          <t>左臂J5以速度20执行正向Jog运动到软件限位148度</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>upper_jog_angle_increment</t>
+          <t>upper_jog_angle</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F11" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
         <v>20</v>
       </c>
+      <c r="H11" t="n">
+        <v>148</v>
+      </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>manual</t>
         </is>
       </c>
     </row>
@@ -39555,34 +40032,37 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>右臂J4以速度10步进-30度后回零</t>
+          <t>左臂J6以速度90执行负向Jog运动到软件限位-87度</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>upper_jog_angle_increment</t>
+          <t>upper_jog_angle</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F12" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
         <v>90</v>
       </c>
+      <c r="H12" t="n">
+        <v>-87</v>
+      </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>manual</t>
         </is>
       </c>
     </row>
@@ -39592,34 +40072,37 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>右臂J5以速度10步进30度后回零</t>
+          <t>左臂J6以速度100执行正向Jog运动到软件限位42度</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>upper_jog_angle_increment</t>
+          <t>upper_jog_angle</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
         <v>100</v>
       </c>
+      <c r="H13" t="n">
+        <v>42</v>
+      </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>manual</t>
         </is>
       </c>
     </row>
@@ -39629,34 +40112,37 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>右臂J6以速度10步进30度后回零</t>
+          <t>左臂J7以速度50执行负向Jog运动到软件限位-80度</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>upper_jog_angle_increment</t>
+          <t>upper_jog_angle</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F14" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
         <v>50</v>
       </c>
+      <c r="H14" t="n">
+        <v>-80</v>
+      </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>manual</t>
         </is>
       </c>
     </row>
@@ -39666,34 +40152,37 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>右臂J7以速度10步进30度后回零</t>
+          <t>左臂J7以速度60执行正向Jog运动到软件限位92度</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>upper_jog_angle_increment</t>
+          <t>upper_jog_angle</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="E15" t="n">
         <v>7</v>
       </c>
       <c r="F15" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
       </c>
+      <c r="H15" t="n">
+        <v>92</v>
+      </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>manual</t>
         </is>
       </c>
     </row>
@@ -39703,34 +40192,37 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>双臂J1以速度10步进30度后回零</t>
+          <t>右臂J1以速度70执行负向Jog运动到软件限位-150度</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>upper_jog_angle_increment</t>
+          <t>upper_jog_angle</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>right</t>
         </is>
       </c>
       <c r="E16" t="n">
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
         <v>70</v>
       </c>
+      <c r="H16" t="n">
+        <v>-150</v>
+      </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>manual</t>
         </is>
       </c>
     </row>
@@ -39740,34 +40232,37 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>双臂J2以速度10步进30度后回零</t>
+          <t>右臂J1以速度80执行正向Jog运动到软件限位176度</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>upper_jog_angle_increment</t>
+          <t>upper_jog_angle</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>right</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
         <v>80</v>
       </c>
+      <c r="H17" t="n">
+        <v>176</v>
+      </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>manual</t>
         </is>
       </c>
     </row>
@@ -39777,34 +40272,37 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>双臂J3以速度10步进30度后回零</t>
+          <t>右臂J2以速度10执行负向Jog运动到软件限位-72度</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>upper_jog_angle_increment</t>
+          <t>upper_jog_angle</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>right</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F18" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
         <v>10</v>
       </c>
+      <c r="H18" t="n">
+        <v>-72</v>
+      </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>manual</t>
         </is>
       </c>
     </row>
@@ -39814,34 +40312,37 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>双臂J4以速度10步进-30度后回零</t>
+          <t>右臂J2以速度20执行正向Jog运动到软件限位125度</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>upper_jog_angle_increment</t>
+          <t>upper_jog_angle</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>right</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F19" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
         <v>20</v>
       </c>
+      <c r="H19" t="n">
+        <v>125</v>
+      </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>manual</t>
         </is>
       </c>
     </row>
@@ -39851,34 +40352,37 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>双臂J5以速度10步进30度后回零</t>
+          <t>右臂J3以速度1执行负向Jog运动到软件限位-163度</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>upper_jog_angle_increment</t>
+          <t>upper_jog_angle</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>right</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F20" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
       </c>
+      <c r="H20" t="n">
+        <v>-163</v>
+      </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>manual</t>
         </is>
       </c>
     </row>
@@ -39888,34 +40392,37 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>双臂J6以速度10步进30度后回零</t>
+          <t>右臂J3以速度20执行正向Jog运动到软件限位167度</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>upper_jog_angle_increment</t>
+          <t>upper_jog_angle</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>right</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F21" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
+      <c r="H21" t="n">
+        <v>167</v>
+      </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>manual</t>
         </is>
       </c>
     </row>
@@ -39925,34 +40432,37 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>双臂J7以速度10步进30度后回零</t>
+          <t>右臂J4以速度50执行负向Jog运动到软件限位-149度</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>upper_jog_angle_increment</t>
+          <t>upper_jog_angle</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>right</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F22" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
         <v>50</v>
       </c>
+      <c r="H22" t="n">
+        <v>-149</v>
+      </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>manual</t>
         </is>
       </c>
     </row>
@@ -39962,34 +40472,37 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>左臂J1步进-327度，验证超限完整行程326度</t>
+          <t>右臂J4以速度60执行正向Jog运动到软件限位1度</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>upper_jog_angle_increment</t>
+          <t>upper_jog_angle</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F23" t="n">
-        <v>-327</v>
+        <v>1</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
       </c>
       <c r="H23" t="n">
-        <v>326</v>
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>range_exception</t>
+          <t>manual</t>
         </is>
       </c>
     </row>
@@ -39999,34 +40512,37 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>左臂J1步进327度，验证超限完整行程326度</t>
+          <t>右臂J5以速度80执行负向Jog运动到软件限位-179度</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>upper_jog_angle_increment</t>
+          <t>upper_jog_angle</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F24" t="n">
-        <v>327</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>80</v>
       </c>
       <c r="H24" t="n">
-        <v>326</v>
+        <v>-179</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>range_exception</t>
+          <t>manual</t>
         </is>
       </c>
     </row>
@@ -40036,34 +40552,37 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>左臂J2步进-198度，验证超限完整行程197度</t>
+          <t>右臂J5以速度40执行正向Jog运动到软件限位148度</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>upper_jog_angle_increment</t>
+          <t>upper_jog_angle</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F25" t="n">
-        <v>-198</v>
+        <v>1</v>
       </c>
       <c r="G25" t="n">
         <v>40</v>
       </c>
       <c r="H25" t="n">
-        <v>197</v>
+        <v>148</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>range_exception</t>
+          <t>manual</t>
         </is>
       </c>
     </row>
@@ -40073,34 +40592,37 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>左臂J2步进198度，验证超限完整行程197度</t>
+          <t>右臂J6以速度30执行负向Jog运动到软件限位-87度</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>upper_jog_angle_increment</t>
+          <t>upper_jog_angle</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F26" t="n">
-        <v>198</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
         <v>30</v>
       </c>
       <c r="H26" t="n">
-        <v>197</v>
+        <v>-87</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>range_exception</t>
+          <t>manual</t>
         </is>
       </c>
     </row>
@@ -40110,34 +40632,37 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>左臂J3步进-331度，验证超限完整行程330度</t>
+          <t>右臂J6以速度20执行正向Jog运动到软件限位42度</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>upper_jog_angle_increment</t>
+          <t>upper_jog_angle</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F27" t="n">
-        <v>-331</v>
+        <v>1</v>
       </c>
       <c r="G27" t="n">
         <v>20</v>
       </c>
       <c r="H27" t="n">
-        <v>330</v>
+        <v>42</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>range_exception</t>
+          <t>manual</t>
         </is>
       </c>
     </row>
@@ -40147,34 +40672,37 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>左臂J3步进331度，验证超限完整行程330度</t>
+          <t>右臂J7以速度10执行负向Jog运动到软件限位-80度</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>upper_jog_angle_increment</t>
+          <t>upper_jog_angle</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F28" t="n">
-        <v>331</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
         <v>10</v>
       </c>
       <c r="H28" t="n">
-        <v>330</v>
+        <v>-80</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>range_exception</t>
+          <t>manual</t>
         </is>
       </c>
     </row>
@@ -40184,34 +40712,37 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>左臂J4步进-151度，验证超限完整行程150度</t>
+          <t>右臂J7以速度26执行正向Jog运动到软件限位92度</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>upper_jog_angle_increment</t>
+          <t>upper_jog_angle</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F29" t="n">
-        <v>-151</v>
+        <v>1</v>
       </c>
       <c r="G29" t="n">
         <v>26</v>
       </c>
       <c r="H29" t="n">
-        <v>150</v>
+        <v>92</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>range_exception</t>
+          <t>manual</t>
         </is>
       </c>
     </row>
@@ -40221,34 +40752,37 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>左臂J4步进151度，验证超限完整行程150度</t>
+          <t>双臂J1以速度35执行负向Jog运动到软件限位-150度</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>upper_jog_angle_increment</t>
+          <t>upper_jog_angle</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>both</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
         <v>35</v>
       </c>
       <c r="H30" t="n">
-        <v>150</v>
+        <v>-150</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>range_exception</t>
+          <t>manual</t>
         </is>
       </c>
     </row>
@@ -40258,34 +40792,37 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>左臂J5步进-328度，验证超限完整行程327度</t>
+          <t>双臂J1以速度41执行正向Jog运动到软件限位176度</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>upper_jog_angle_increment</t>
+          <t>upper_jog_angle</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>both</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>-328</v>
+        <v>1</v>
       </c>
       <c r="G31" t="n">
         <v>41</v>
       </c>
       <c r="H31" t="n">
-        <v>327</v>
+        <v>176</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>range_exception</t>
+          <t>manual</t>
         </is>
       </c>
     </row>
@@ -40295,34 +40832,37 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>左臂J5步进328度，验证超限完整行程327度</t>
+          <t>双臂J2以速度10执行负向Jog运动到软件限位-72度</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>upper_jog_angle_increment</t>
+          <t>upper_jog_angle</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>both</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F32" t="n">
-        <v>328</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
         <v>10</v>
       </c>
       <c r="H32" t="n">
-        <v>327</v>
+        <v>-72</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>range_exception</t>
+          <t>manual</t>
         </is>
       </c>
     </row>
@@ -40332,34 +40872,37 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>左臂J6步进-130度，验证超限完整行程129度</t>
+          <t>双臂J3以速度50执行负向Jog运动到软件限位-163度</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>upper_jog_angle_increment</t>
+          <t>upper_jog_angle</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>both</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F33" t="n">
-        <v>-130</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H33" t="n">
-        <v>129</v>
+        <v>-163</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>range_exception</t>
+          <t>manual</t>
         </is>
       </c>
     </row>
@@ -40369,34 +40912,37 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>左臂J6步进130度，验证超限完整行程129度</t>
+          <t>双臂J3以速度60执行正向Jog运动到软件限位167度</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>upper_jog_angle_increment</t>
+          <t>upper_jog_angle</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>both</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F34" t="n">
-        <v>130</v>
+        <v>1</v>
       </c>
       <c r="G34" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H34" t="n">
-        <v>129</v>
+        <v>167</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>range_exception</t>
+          <t>manual</t>
         </is>
       </c>
     </row>
@@ -40406,34 +40952,37 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>左臂J7步进-173度，验证超限完整行程172度</t>
+          <t>双臂J4以速度80执行负向Jog运动到软件限位-149度</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>upper_jog_angle_increment</t>
+          <t>upper_jog_angle</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>both</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F35" t="n">
-        <v>-173</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="H35" t="n">
-        <v>172</v>
+        <v>-149</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>range_exception</t>
+          <t>manual</t>
         </is>
       </c>
     </row>
@@ -40443,34 +40992,37 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>左臂J7步进173度，验证超限完整行程172度</t>
+          <t>双臂J4以速度40执行正向Jog运动到软件限位1度</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>upper_jog_angle_increment</t>
+          <t>upper_jog_angle</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>both</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F36" t="n">
-        <v>173</v>
+        <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="H36" t="n">
-        <v>172</v>
+        <v>1</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>range_exception</t>
+          <t>manual</t>
         </is>
       </c>
     </row>
@@ -40480,34 +41032,37 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>右臂J1步进-327度，验证超限完整行程326度</t>
+          <t>双臂J5以速度30执行负向Jog运动到软件限位-179度</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>upper_jog_angle_increment</t>
+          <t>upper_jog_angle</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>both</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F37" t="n">
-        <v>-327</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H37" t="n">
-        <v>326</v>
+        <v>-179</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>range_exception</t>
+          <t>manual</t>
         </is>
       </c>
     </row>
@@ -40517,34 +41072,37 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>右臂J1步进327度，验证超限完整行程326度</t>
+          <t>双臂J5以速度20执行正向Jog运动到软件限位148度</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>upper_jog_angle_increment</t>
+          <t>upper_jog_angle</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>both</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F38" t="n">
-        <v>327</v>
+        <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H38" t="n">
-        <v>326</v>
+        <v>148</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>range_exception</t>
+          <t>manual</t>
         </is>
       </c>
     </row>
@@ -40554,34 +41112,37 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>右臂J2步进-198度，验证超限完整行程197度</t>
+          <t>双臂J6以速度10执行负向Jog运动到软件限位-87度</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>upper_jog_angle_increment</t>
+          <t>upper_jog_angle</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>both</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F39" t="n">
-        <v>-198</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H39" t="n">
-        <v>197</v>
+        <v>-87</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>range_exception</t>
+          <t>manual</t>
         </is>
       </c>
     </row>
@@ -40591,34 +41152,37 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>右臂J2步进198度，验证超限完整行程197度</t>
+          <t>双臂J6以速度26执行正向Jog运动到软件限位42度</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>upper_jog_angle_increment</t>
+          <t>upper_jog_angle</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>both</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F40" t="n">
-        <v>198</v>
+        <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="H40" t="n">
-        <v>197</v>
+        <v>42</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>range_exception</t>
+          <t>manual</t>
         </is>
       </c>
     </row>
@@ -40628,34 +41192,37 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>右臂J3步进-331度，验证超限完整行程330度</t>
+          <t>双臂J7以速度35执行负向Jog运动到软件限位-80度</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>upper_jog_angle_increment</t>
+          <t>upper_jog_angle</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>both</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F41" t="n">
-        <v>-331</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="H41" t="n">
-        <v>330</v>
+        <v>-80</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>range_exception</t>
+          <t>manual</t>
         </is>
       </c>
     </row>
@@ -40665,34 +41232,37 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>右臂J3步进331度，验证超限完整行程330度</t>
+          <t>双臂J7以速度41执行正向Jog运动到软件限位92度</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>upper_jog_angle_increment</t>
+          <t>upper_jog_angle</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>both</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F42" t="n">
-        <v>331</v>
+        <v>1</v>
       </c>
       <c r="G42" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="H42" t="n">
-        <v>330</v>
+        <v>92</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>range_exception</t>
+          <t>manual</t>
         </is>
       </c>
     </row>
@@ -40702,34 +41272,36 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>右臂J4步进-151度，验证超限完整行程150度</t>
+          <t>左臂刷新模式下调用J1正向Jog运动，验证返回失败并提示切换插补模式</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>upper_jog_angle_increment</t>
+          <t>upper_jog_angle</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F43" t="n">
-        <v>-151</v>
+        <v>1</v>
       </c>
       <c r="G43" t="n">
-        <v>60</v>
-      </c>
-      <c r="H43" t="n">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>range_exception</t>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>刷新模式无法使用JOG运动</t>
         </is>
       </c>
     </row>
@@ -40739,34 +41311,31 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>右臂J4步进151度，验证超限完整行程150度</t>
+          <t>左臂J7速度为0，验证速度超限</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>upper_jog_angle_increment</t>
+          <t>upper_jog_angle</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F44" t="n">
-        <v>151</v>
+        <v>1</v>
       </c>
       <c r="G44" t="n">
-        <v>80</v>
-      </c>
-      <c r="H44" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>range_exception</t>
+          <t>exception</t>
         </is>
       </c>
     </row>
@@ -40776,34 +41345,31 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>右臂J5步进-328度，验证超限完整行程327度</t>
+          <t>左臂J7速度为101，验证速度超限</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>upper_jog_angle_increment</t>
+          <t>upper_jog_angle</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F45" t="n">
-        <v>-328</v>
+        <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>90</v>
-      </c>
-      <c r="H45" t="n">
-        <v>327</v>
+        <v>101</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>range_exception</t>
+          <t>exception</t>
         </is>
       </c>
     </row>
@@ -40813,34 +41379,31 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>右臂J5步进328度，验证超限完整行程327度</t>
+          <t>左臂关节ID为0，验证关节ID超限</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>upper_jog_angle_increment</t>
+          <t>upper_jog_angle</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>328</v>
+        <v>1</v>
       </c>
       <c r="G46" t="n">
-        <v>20</v>
-      </c>
-      <c r="H46" t="n">
-        <v>327</v>
+        <v>10</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>range_exception</t>
+          <t>exception</t>
         </is>
       </c>
     </row>
@@ -40850,34 +41413,31 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>右臂J6步进-130度，验证超限完整行程129度</t>
+          <t>左臂J7方向为-1，验证方向超限</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>upper_jog_angle_increment</t>
+          <t>upper_jog_angle</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F47" t="n">
-        <v>-130</v>
+        <v>-1</v>
       </c>
       <c r="G47" t="n">
-        <v>100</v>
-      </c>
-      <c r="H47" t="n">
-        <v>129</v>
+        <v>10</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>range_exception</t>
+          <t>exception</t>
         </is>
       </c>
     </row>
@@ -40887,34 +41447,31 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>右臂J6步进130度，验证超限完整行程129度</t>
+          <t>左臂J7方向为2，验证方向超限</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>upper_jog_angle_increment</t>
+          <t>upper_jog_angle</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F48" t="n">
-        <v>130</v>
+        <v>2</v>
       </c>
       <c r="G48" t="n">
-        <v>60</v>
-      </c>
-      <c r="H48" t="n">
-        <v>129</v>
+        <v>10</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>range_exception</t>
+          <t>exception</t>
         </is>
       </c>
     </row>
@@ -40924,12 +41481,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>右臂J7步进-173度，验证超限完整行程172度</t>
+          <t>右臂J7速度为0，验证速度超限</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>upper_jog_angle_increment</t>
+          <t>upper_jog_angle</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -40941,17 +41498,14 @@
         <v>7</v>
       </c>
       <c r="F49" t="n">
-        <v>-173</v>
+        <v>1</v>
       </c>
       <c r="G49" t="n">
-        <v>20</v>
-      </c>
-      <c r="H49" t="n">
-        <v>172</v>
+        <v>0</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>range_exception</t>
+          <t>exception</t>
         </is>
       </c>
     </row>
@@ -40961,12 +41515,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>右臂J7步进173度，验证超限完整行程172度</t>
+          <t>右臂J7速度为101，验证速度超限</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>upper_jog_angle_increment</t>
+          <t>upper_jog_angle</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -40978,17 +41532,14 @@
         <v>7</v>
       </c>
       <c r="F50" t="n">
-        <v>173</v>
+        <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>40</v>
-      </c>
-      <c r="H50" t="n">
-        <v>172</v>
+        <v>101</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>range_exception</t>
+          <t>exception</t>
         </is>
       </c>
     </row>
@@ -40998,34 +41549,31 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>双臂J1步进-327度，验证超限完整行程326度</t>
+          <t>右臂关节ID为0，验证关节ID超限</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>upper_jog_angle_increment</t>
+          <t>upper_jog_angle</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>right</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>-327</v>
+        <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>50</v>
-      </c>
-      <c r="H51" t="n">
-        <v>326</v>
+        <v>10</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>range_exception</t>
+          <t>exception</t>
         </is>
       </c>
     </row>
@@ -41035,34 +41583,31 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>双臂J1步进327度，验证超限完整行程326度</t>
+          <t>右臂J7方向为-1，验证方向超限</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>upper_jog_angle_increment</t>
+          <t>upper_jog_angle</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>right</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F52" t="n">
-        <v>327</v>
+        <v>-1</v>
       </c>
       <c r="G52" t="n">
-        <v>60</v>
-      </c>
-      <c r="H52" t="n">
-        <v>326</v>
+        <v>10</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>range_exception</t>
+          <t>exception</t>
         </is>
       </c>
     </row>
@@ -41072,34 +41617,31 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>双臂J2步进-198度，验证超限完整行程197度</t>
+          <t>右臂J7方向为2，验证方向超限</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>upper_jog_angle_increment</t>
+          <t>upper_jog_angle</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>right</t>
         </is>
       </c>
       <c r="E53" t="n">
+        <v>7</v>
+      </c>
+      <c r="F53" t="n">
         <v>2</v>
       </c>
-      <c r="F53" t="n">
-        <v>-198</v>
-      </c>
       <c r="G53" t="n">
-        <v>70</v>
-      </c>
-      <c r="H53" t="n">
-        <v>197</v>
+        <v>10</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>range_exception</t>
+          <t>exception</t>
         </is>
       </c>
     </row>
@@ -41109,12 +41651,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>双臂J2步进198度，验证超限完整行程197度</t>
+          <t>双臂J7速度为0，验证速度超限</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>upper_jog_angle_increment</t>
+          <t>upper_jog_angle</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -41123,20 +41665,17 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F54" t="n">
-        <v>198</v>
+        <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>40</v>
-      </c>
-      <c r="H54" t="n">
-        <v>197</v>
+        <v>0</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>range_exception</t>
+          <t>exception</t>
         </is>
       </c>
     </row>
@@ -41146,12 +41685,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>双臂J3步进-331度，验证超限完整行程330度</t>
+          <t>双臂J7速度为101，验证速度超限</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>upper_jog_angle_increment</t>
+          <t>upper_jog_angle</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -41160,20 +41699,17 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F55" t="n">
-        <v>-331</v>
+        <v>1</v>
       </c>
       <c r="G55" t="n">
-        <v>60</v>
-      </c>
-      <c r="H55" t="n">
-        <v>330</v>
+        <v>101</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>range_exception</t>
+          <t>exception</t>
         </is>
       </c>
     </row>
@@ -41183,12 +41719,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>双臂J3步进331度，验证超限完整行程330度</t>
+          <t>双臂关节ID为0，验证关节ID超限</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>upper_jog_angle_increment</t>
+          <t>upper_jog_angle</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -41197,20 +41733,17 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>331</v>
+        <v>1</v>
       </c>
       <c r="G56" t="n">
-        <v>70</v>
-      </c>
-      <c r="H56" t="n">
-        <v>330</v>
+        <v>10</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>range_exception</t>
+          <t>exception</t>
         </is>
       </c>
     </row>
@@ -41220,12 +41753,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>双臂J4步进-151度，验证超限完整行程150度</t>
+          <t>双臂J7方向为-1，验证方向超限</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>upper_jog_angle_increment</t>
+          <t>upper_jog_angle</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -41234,20 +41767,17 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F57" t="n">
-        <v>-151</v>
+        <v>-1</v>
       </c>
       <c r="G57" t="n">
-        <v>80</v>
-      </c>
-      <c r="H57" t="n">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>range_exception</t>
+          <t>exception</t>
         </is>
       </c>
     </row>
@@ -41257,12 +41787,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>双臂J4步进151度，验证超限完整行程150度</t>
+          <t>双臂J7方向为2，验证方向超限</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>upper_jog_angle_increment</t>
+          <t>upper_jog_angle</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -41271,587 +41801,17 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F58" t="n">
-        <v>151</v>
+        <v>2</v>
       </c>
       <c r="G58" t="n">
-        <v>30</v>
-      </c>
-      <c r="H58" t="n">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>range_exception</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>58</v>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>双臂J5步进-328度，验证超限完整行程327度</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>upper_jog_angle_increment</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="E59" t="n">
-        <v>5</v>
-      </c>
-      <c r="F59" t="n">
-        <v>-328</v>
-      </c>
-      <c r="G59" t="n">
-        <v>50</v>
-      </c>
-      <c r="H59" t="n">
-        <v>327</v>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>range_exception</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>59</v>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>双臂J5步进328度，验证超限完整行程327度</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>upper_jog_angle_increment</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
-        <v>5</v>
-      </c>
-      <c r="F60" t="n">
-        <v>328</v>
-      </c>
-      <c r="G60" t="n">
-        <v>40</v>
-      </c>
-      <c r="H60" t="n">
-        <v>327</v>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>range_exception</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>60</v>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>双臂J6步进-130度，验证超限完整行程129度</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>upper_jog_angle_increment</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
-        <v>6</v>
-      </c>
-      <c r="F61" t="n">
-        <v>-130</v>
-      </c>
-      <c r="G61" t="n">
-        <v>20</v>
-      </c>
-      <c r="H61" t="n">
-        <v>129</v>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>range_exception</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>61</v>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>双臂J6步进130度，验证超限完整行程129度</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>upper_jog_angle_increment</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
-        <v>6</v>
-      </c>
-      <c r="F62" t="n">
-        <v>130</v>
-      </c>
-      <c r="G62" t="n">
-        <v>40</v>
-      </c>
-      <c r="H62" t="n">
-        <v>129</v>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>range_exception</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>62</v>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>双臂J7步进-173度，验证超限完整行程172度</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>upper_jog_angle_increment</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v>7</v>
-      </c>
-      <c r="F63" t="n">
-        <v>-173</v>
-      </c>
-      <c r="G63" t="n">
-        <v>80</v>
-      </c>
-      <c r="H63" t="n">
-        <v>172</v>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>range_exception</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>63</v>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>双臂J7步进173度，验证超限完整行程172度</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>upper_jog_angle_increment</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>7</v>
-      </c>
-      <c r="F64" t="n">
-        <v>173</v>
-      </c>
-      <c r="G64" t="n">
-        <v>20</v>
-      </c>
-      <c r="H64" t="n">
-        <v>172</v>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>range_exception</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>64</v>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>左臂J7速度为0，验证速度超限</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>upper_jog_angle_increment</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>7</v>
-      </c>
-      <c r="F65" t="n">
-        <v>30</v>
-      </c>
-      <c r="G65" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
           <t>exception</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>65</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>左臂J7速度为101，验证速度超限</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>upper_jog_angle_increment</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="E66" t="n">
-        <v>7</v>
-      </c>
-      <c r="F66" t="n">
-        <v>30</v>
-      </c>
-      <c r="G66" t="n">
-        <v>101</v>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>exception</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>66</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>左臂关节ID为0，验证关节ID超限</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>upper_jog_angle_increment</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="E67" t="n">
-        <v>0</v>
-      </c>
-      <c r="F67" t="n">
-        <v>30</v>
-      </c>
-      <c r="G67" t="n">
-        <v>10</v>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>exception</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>67</v>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>右臂J7速度为0，验证速度超限</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>upper_jog_angle_increment</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="E68" t="n">
-        <v>7</v>
-      </c>
-      <c r="F68" t="n">
-        <v>30</v>
-      </c>
-      <c r="G68" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>exception</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>68</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>右臂J7速度为101，验证速度超限</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>upper_jog_angle_increment</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="E69" t="n">
-        <v>7</v>
-      </c>
-      <c r="F69" t="n">
-        <v>30</v>
-      </c>
-      <c r="G69" t="n">
-        <v>101</v>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>exception</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>69</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>右臂关节ID为0，验证关节ID超限</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>upper_jog_angle_increment</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="E70" t="n">
-        <v>0</v>
-      </c>
-      <c r="F70" t="n">
-        <v>30</v>
-      </c>
-      <c r="G70" t="n">
-        <v>10</v>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>exception</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>70</v>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>双臂J7速度为0，验证速度超限</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>upper_jog_angle_increment</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="E71" t="n">
-        <v>7</v>
-      </c>
-      <c r="F71" t="n">
-        <v>30</v>
-      </c>
-      <c r="G71" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>exception</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>71</v>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>双臂J7速度为101，验证速度超限</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>upper_jog_angle_increment</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="E72" t="n">
-        <v>7</v>
-      </c>
-      <c r="F72" t="n">
-        <v>30</v>
-      </c>
-      <c r="G72" t="n">
-        <v>101</v>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>exception</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>72</v>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>双臂关节ID为0，验证关节ID超限</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>upper_jog_angle_increment</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="E73" t="n">
-        <v>0</v>
-      </c>
-      <c r="F73" t="n">
-        <v>30</v>
-      </c>
-      <c r="G73" t="n">
-        <v>10</v>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>exception</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>73</v>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>左臂刷新模式下调用J1正向步进30度，验证返回失败并提示切换插补模式</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>upper_jog_angle_increment</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="E74" t="n">
-        <v>1</v>
-      </c>
-      <c r="F74" t="n">
-        <v>30</v>
-      </c>
-      <c r="G74" t="n">
-        <v>10</v>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>unsupported</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>刷新模式无法使用JOG运动</t>
         </is>
       </c>
     </row>

--- a/test_data/upper_body.xlsx
+++ b/test_data/upper_body.xlsx
@@ -28796,7 +28796,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>设置上半身关节最小角度，joint_id=1，degree=-150.0</t>
+          <t>设置上半身关节最小角度：joint_id=1，degree=-150.0</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -28825,7 +28825,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>设置上半身关节最小角度，joint_id=1，degree=-68.0</t>
+          <t>设置上半身关节最小角度：joint_id=1，degree=-68.5</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -28837,7 +28837,7 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>-68</v>
+        <v>-68.5</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -28854,7 +28854,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>设置上半身关节最小角度，joint_id=1，degree=0.0</t>
+          <t>设置上半身关节最小角度：joint_id=1，degree=13.0</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -28866,7 +28866,7 @@
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -28883,7 +28883,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>设置上半身关节最小角度，joint_id=1，degree=94.0</t>
+          <t>设置上半身关节最小角度：joint_id=1，degree=94.5</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -28895,7 +28895,7 @@
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>94</v>
+        <v>94.5</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
@@ -28912,7 +28912,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>设置上半身关节最小角度，joint_id=1，degree=176.0</t>
+          <t>设置上半身关节最小角度：joint_id=1，degree=176.0</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -28941,7 +28941,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>设置上半身关节最小角度，joint_id=2，degree=-72.0</t>
+          <t>设置上半身关节最小角度：joint_id=2，degree=-65.0</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -28953,7 +28953,7 @@
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>-72</v>
+        <v>-65</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
@@ -28970,7 +28970,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>设置上半身关节最小角度，joint_id=2，degree=-23.0</t>
+          <t>设置上半身关节最小角度：joint_id=2，degree=-21.2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -28982,7 +28982,7 @@
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>-23</v>
+        <v>-21.2</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
@@ -28999,7 +28999,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>设置上半身关节最小角度，joint_id=2，degree=0.0</t>
+          <t>设置上半身关节最小角度：joint_id=2，degree=22.5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -29011,7 +29011,7 @@
         <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>22.5</v>
       </c>
       <c r="F9" t="n">
         <v>1</v>
@@ -29028,7 +29028,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>设置上半身关节最小角度，joint_id=2，degree=76.0</t>
+          <t>设置上半身关节最小角度：joint_id=2，degree=66.2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -29040,7 +29040,7 @@
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>76</v>
+        <v>66.2</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
@@ -29057,7 +29057,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>设置上半身关节最小角度，joint_id=2，degree=125.0</t>
+          <t>设置上半身关节最小角度：joint_id=2，degree=110.0</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -29069,7 +29069,7 @@
         <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
@@ -29086,7 +29086,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>设置上半身关节最小角度，joint_id=3，degree=-163.0</t>
+          <t>设置上半身关节最小角度：joint_id=3，degree=-165.0</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -29098,7 +29098,7 @@
         <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>-163</v>
+        <v>-165</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
@@ -29115,7 +29115,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>设置上半身关节最小角度，joint_id=3，degree=-80.0</t>
+          <t>设置上半身关节最小角度：joint_id=3，degree=-82.5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -29127,7 +29127,7 @@
         <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>-80</v>
+        <v>-82.5</v>
       </c>
       <c r="F13" t="n">
         <v>1</v>
@@ -29144,7 +29144,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>设置上半身关节最小角度，joint_id=3，degree=0.0</t>
+          <t>设置上半身关节最小角度：joint_id=3，degree=0.0</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -29173,7 +29173,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>设置上半身关节最小角度，joint_id=3，degree=84.0</t>
+          <t>设置上半身关节最小角度：joint_id=3，degree=82.5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -29185,7 +29185,7 @@
         <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>84</v>
+        <v>82.5</v>
       </c>
       <c r="F15" t="n">
         <v>1</v>
@@ -29202,7 +29202,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>设置上半身关节最小角度，joint_id=3，degree=167.0</t>
+          <t>设置上半身关节最小角度：joint_id=3，degree=165.0</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -29214,7 +29214,7 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F16" t="n">
         <v>1</v>
@@ -29231,7 +29231,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>设置上半身关节最小角度，joint_id=4，degree=-149.0</t>
+          <t>设置上半身关节最小角度：joint_id=4，degree=-164.0</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -29243,7 +29243,7 @@
         <v>4</v>
       </c>
       <c r="E17" t="n">
-        <v>-149</v>
+        <v>-164</v>
       </c>
       <c r="F17" t="n">
         <v>1</v>
@@ -29260,7 +29260,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>设置上半身关节最小角度，joint_id=4，degree=-112.0</t>
+          <t>设置上半身关节最小角度：joint_id=4，degree=-125.5</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -29272,7 +29272,7 @@
         <v>4</v>
       </c>
       <c r="E18" t="n">
-        <v>-112</v>
+        <v>-125.5</v>
       </c>
       <c r="F18" t="n">
         <v>1</v>
@@ -29289,7 +29289,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>设置上半身关节最小角度，joint_id=4，degree=-36.0</t>
+          <t>设置上半身关节最小角度：joint_id=4，degree=-87.0</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -29301,7 +29301,7 @@
         <v>4</v>
       </c>
       <c r="E19" t="n">
-        <v>-36</v>
+        <v>-87</v>
       </c>
       <c r="F19" t="n">
         <v>1</v>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>设置上半身关节最小角度，joint_id=4，degree=0.0</t>
+          <t>设置上半身关节最小角度：joint_id=4，degree=-48.5</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -29330,7 +29330,7 @@
         <v>4</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>-48.5</v>
       </c>
       <c r="F20" t="n">
         <v>1</v>
@@ -29347,7 +29347,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>设置上半身关节最小角度，joint_id=4，degree=1.0</t>
+          <t>设置上半身关节最小角度：joint_id=4，degree=-10.0</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -29359,7 +29359,7 @@
         <v>4</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>-10</v>
       </c>
       <c r="F21" t="n">
         <v>1</v>
@@ -29376,7 +29376,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>设置上半身关节最小角度，joint_id=5，degree=-179.0</t>
+          <t>设置上半身关节最小角度：joint_id=5，degree=-165.0</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -29388,7 +29388,7 @@
         <v>5</v>
       </c>
       <c r="E22" t="n">
-        <v>-179</v>
+        <v>-165</v>
       </c>
       <c r="F22" t="n">
         <v>1</v>
@@ -29405,7 +29405,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>设置上半身关节最小角度，joint_id=5，degree=-97.0</t>
+          <t>设置上半身关节最小角度：joint_id=5，degree=-82.5</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -29417,7 +29417,7 @@
         <v>5</v>
       </c>
       <c r="E23" t="n">
-        <v>-97</v>
+        <v>-82.5</v>
       </c>
       <c r="F23" t="n">
         <v>1</v>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>设置上半身关节最小角度，joint_id=5，degree=0.0</t>
+          <t>设置上半身关节最小角度：joint_id=5，degree=0.0</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -29463,7 +29463,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>设置上半身关节最小角度，joint_id=5，degree=66.0</t>
+          <t>设置上半身关节最小角度：joint_id=5，degree=82.5</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -29475,7 +29475,7 @@
         <v>5</v>
       </c>
       <c r="E25" t="n">
-        <v>66</v>
+        <v>82.5</v>
       </c>
       <c r="F25" t="n">
         <v>1</v>
@@ -29492,7 +29492,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>设置上半身关节最小角度，joint_id=5，degree=148.0</t>
+          <t>设置上半身关节最小角度：joint_id=5，degree=165.0</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -29504,7 +29504,7 @@
         <v>5</v>
       </c>
       <c r="E26" t="n">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="F26" t="n">
         <v>1</v>
@@ -29521,7 +29521,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>设置上半身关节最小角度，joint_id=6，degree=-87.0</t>
+          <t>设置上半身关节最小角度：joint_id=6，degree=-75.0</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -29533,7 +29533,7 @@
         <v>6</v>
       </c>
       <c r="E27" t="n">
-        <v>-87</v>
+        <v>-75</v>
       </c>
       <c r="F27" t="n">
         <v>1</v>
@@ -29550,7 +29550,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>设置上半身关节最小角度，joint_id=6，degree=-55.0</t>
+          <t>设置上半身关节最小角度：joint_id=6，degree=-45.0</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -29562,7 +29562,7 @@
         <v>6</v>
       </c>
       <c r="E28" t="n">
-        <v>-55</v>
+        <v>-45</v>
       </c>
       <c r="F28" t="n">
         <v>1</v>
@@ -29579,7 +29579,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>设置上半身关节最小角度，joint_id=6，degree=0.0</t>
+          <t>设置上半身关节最小角度：joint_id=6，degree=-15.0</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -29591,7 +29591,7 @@
         <v>6</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="F29" t="n">
         <v>1</v>
@@ -29608,7 +29608,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>设置上半身关节最小角度，joint_id=6，degree=10.0</t>
+          <t>设置上半身关节最小角度：joint_id=6，degree=15.0</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -29620,7 +29620,7 @@
         <v>6</v>
       </c>
       <c r="E30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F30" t="n">
         <v>1</v>
@@ -29637,7 +29637,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>设置上半身关节最小角度，joint_id=6，degree=42.0</t>
+          <t>设置上半身关节最小角度：joint_id=6，degree=45.0</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -29649,7 +29649,7 @@
         <v>6</v>
       </c>
       <c r="E31" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F31" t="n">
         <v>1</v>
@@ -29666,7 +29666,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>设置上半身关节最小角度，joint_id=7，degree=-80.0</t>
+          <t>设置上半身关节最小角度：joint_id=7，degree=-80.0</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -29695,7 +29695,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>设置上半身关节最小角度，joint_id=7，degree=-37.0</t>
+          <t>设置上半身关节最小角度：joint_id=7，degree=-41.2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -29707,7 +29707,7 @@
         <v>7</v>
       </c>
       <c r="E33" t="n">
-        <v>-37</v>
+        <v>-41.2</v>
       </c>
       <c r="F33" t="n">
         <v>1</v>
@@ -29724,7 +29724,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>设置上半身关节最小角度，joint_id=7，degree=0.0</t>
+          <t>设置上半身关节最小角度：joint_id=7，degree=-2.5</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -29736,7 +29736,7 @@
         <v>7</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>-2.5</v>
       </c>
       <c r="F34" t="n">
         <v>1</v>
@@ -29753,7 +29753,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>设置上半身关节最小角度，joint_id=7，degree=49.0</t>
+          <t>设置上半身关节最小角度：joint_id=7，degree=36.2</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -29765,7 +29765,7 @@
         <v>7</v>
       </c>
       <c r="E35" t="n">
-        <v>49</v>
+        <v>36.2</v>
       </c>
       <c r="F35" t="n">
         <v>1</v>
@@ -29782,7 +29782,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>设置上半身关节最小角度，joint_id=7，degree=92.0</t>
+          <t>设置上半身关节最小角度：joint_id=7，degree=75.0</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -29794,7 +29794,7 @@
         <v>7</v>
       </c>
       <c r="E36" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="F36" t="n">
         <v>1</v>
@@ -29966,7 +29966,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>设置上半身关节最大角度，joint_id=1，degree=-150.0</t>
+          <t>设置上半身关节最大角度：joint_id=1，degree=-150.0</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -29995,7 +29995,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>设置上半身关节最大角度，joint_id=1，degree=-68.0</t>
+          <t>设置上半身关节最大角度：joint_id=1，degree=-68.5</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -30007,7 +30007,7 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>-68</v>
+        <v>-68.5</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -30024,7 +30024,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>设置上半身关节最大角度，joint_id=1，degree=0.0</t>
+          <t>设置上半身关节最大角度：joint_id=1，degree=13.0</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -30036,7 +30036,7 @@
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -30053,7 +30053,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>设置上半身关节最大角度，joint_id=1，degree=94.0</t>
+          <t>设置上半身关节最大角度：joint_id=1，degree=94.5</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -30065,7 +30065,7 @@
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>94</v>
+        <v>94.5</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
@@ -30082,7 +30082,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>设置上半身关节最大角度，joint_id=1，degree=176.0</t>
+          <t>设置上半身关节最大角度：joint_id=1，degree=176.0</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -30111,7 +30111,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>设置上半身关节最大角度，joint_id=2，degree=-72.0</t>
+          <t>设置上半身关节最大角度：joint_id=2，degree=-65.0</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -30123,7 +30123,7 @@
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>-72</v>
+        <v>-65</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
@@ -30140,7 +30140,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>设置上半身关节最大角度，joint_id=2，degree=-23.0</t>
+          <t>设置上半身关节最大角度：joint_id=2，degree=-21.2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -30152,7 +30152,7 @@
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>-23</v>
+        <v>-21.2</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
@@ -30169,7 +30169,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>设置上半身关节最大角度，joint_id=2，degree=0.0</t>
+          <t>设置上半身关节最大角度：joint_id=2，degree=22.5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -30181,7 +30181,7 @@
         <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>22.5</v>
       </c>
       <c r="F9" t="n">
         <v>1</v>
@@ -30198,7 +30198,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>设置上半身关节最大角度，joint_id=2，degree=76.0</t>
+          <t>设置上半身关节最大角度：joint_id=2，degree=66.2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -30210,7 +30210,7 @@
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>76</v>
+        <v>66.2</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
@@ -30227,7 +30227,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>设置上半身关节最大角度，joint_id=2，degree=125.0</t>
+          <t>设置上半身关节最大角度：joint_id=2，degree=110.0</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -30239,7 +30239,7 @@
         <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
@@ -30256,7 +30256,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>设置上半身关节最大角度，joint_id=3，degree=-163.0</t>
+          <t>设置上半身关节最大角度：joint_id=3，degree=-165.0</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -30268,7 +30268,7 @@
         <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>-163</v>
+        <v>-165</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
@@ -30285,7 +30285,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>设置上半身关节最大角度，joint_id=3，degree=-80.0</t>
+          <t>设置上半身关节最大角度：joint_id=3，degree=-82.5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -30297,7 +30297,7 @@
         <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>-80</v>
+        <v>-82.5</v>
       </c>
       <c r="F13" t="n">
         <v>1</v>
@@ -30314,7 +30314,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>设置上半身关节最大角度，joint_id=3，degree=0.0</t>
+          <t>设置上半身关节最大角度：joint_id=3，degree=0.0</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -30343,7 +30343,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>设置上半身关节最大角度，joint_id=3，degree=84.0</t>
+          <t>设置上半身关节最大角度：joint_id=3，degree=82.5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -30355,7 +30355,7 @@
         <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>84</v>
+        <v>82.5</v>
       </c>
       <c r="F15" t="n">
         <v>1</v>
@@ -30372,7 +30372,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>设置上半身关节最大角度，joint_id=3，degree=167.0</t>
+          <t>设置上半身关节最大角度：joint_id=3，degree=165.0</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -30384,7 +30384,7 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F16" t="n">
         <v>1</v>
@@ -30401,7 +30401,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>设置上半身关节最大角度，joint_id=4，degree=-149.0</t>
+          <t>设置上半身关节最大角度：joint_id=4，degree=-164.0</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -30413,7 +30413,7 @@
         <v>4</v>
       </c>
       <c r="E17" t="n">
-        <v>-149</v>
+        <v>-164</v>
       </c>
       <c r="F17" t="n">
         <v>1</v>
@@ -30430,7 +30430,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>设置上半身关节最大角度，joint_id=4，degree=-112.0</t>
+          <t>设置上半身关节最大角度：joint_id=4，degree=-125.5</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -30442,7 +30442,7 @@
         <v>4</v>
       </c>
       <c r="E18" t="n">
-        <v>-112</v>
+        <v>-125.5</v>
       </c>
       <c r="F18" t="n">
         <v>1</v>
@@ -30459,7 +30459,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>设置上半身关节最大角度，joint_id=4，degree=-36.0</t>
+          <t>设置上半身关节最大角度：joint_id=4，degree=-87.0</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -30471,7 +30471,7 @@
         <v>4</v>
       </c>
       <c r="E19" t="n">
-        <v>-36</v>
+        <v>-87</v>
       </c>
       <c r="F19" t="n">
         <v>1</v>
@@ -30488,7 +30488,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>设置上半身关节最大角度，joint_id=4，degree=0.0</t>
+          <t>设置上半身关节最大角度：joint_id=4，degree=-48.5</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -30500,7 +30500,7 @@
         <v>4</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>-48.5</v>
       </c>
       <c r="F20" t="n">
         <v>1</v>
@@ -30517,7 +30517,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>设置上半身关节最大角度，joint_id=4，degree=1.0</t>
+          <t>设置上半身关节最大角度：joint_id=4，degree=-10.0</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -30529,7 +30529,7 @@
         <v>4</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>-10</v>
       </c>
       <c r="F21" t="n">
         <v>1</v>
@@ -30546,7 +30546,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>设置上半身关节最大角度，joint_id=5，degree=-179.0</t>
+          <t>设置上半身关节最大角度：joint_id=5，degree=-165.0</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -30558,7 +30558,7 @@
         <v>5</v>
       </c>
       <c r="E22" t="n">
-        <v>-179</v>
+        <v>-165</v>
       </c>
       <c r="F22" t="n">
         <v>1</v>
@@ -30575,7 +30575,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>设置上半身关节最大角度，joint_id=5，degree=-97.0</t>
+          <t>设置上半身关节最大角度：joint_id=5，degree=-82.5</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -30587,7 +30587,7 @@
         <v>5</v>
       </c>
       <c r="E23" t="n">
-        <v>-97</v>
+        <v>-82.5</v>
       </c>
       <c r="F23" t="n">
         <v>1</v>
@@ -30604,7 +30604,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>设置上半身关节最大角度，joint_id=5，degree=0.0</t>
+          <t>设置上半身关节最大角度：joint_id=5，degree=0.0</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -30633,7 +30633,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>设置上半身关节最大角度，joint_id=5，degree=66.0</t>
+          <t>设置上半身关节最大角度：joint_id=5，degree=82.5</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -30645,7 +30645,7 @@
         <v>5</v>
       </c>
       <c r="E25" t="n">
-        <v>66</v>
+        <v>82.5</v>
       </c>
       <c r="F25" t="n">
         <v>1</v>
@@ -30662,7 +30662,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>设置上半身关节最大角度，joint_id=5，degree=148.0</t>
+          <t>设置上半身关节最大角度：joint_id=5，degree=165.0</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -30674,7 +30674,7 @@
         <v>5</v>
       </c>
       <c r="E26" t="n">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="F26" t="n">
         <v>1</v>
@@ -30691,7 +30691,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>设置上半身关节最大角度，joint_id=6，degree=-87.0</t>
+          <t>设置上半身关节最大角度：joint_id=6，degree=-75.0</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -30703,7 +30703,7 @@
         <v>6</v>
       </c>
       <c r="E27" t="n">
-        <v>-87</v>
+        <v>-75</v>
       </c>
       <c r="F27" t="n">
         <v>1</v>
@@ -30720,7 +30720,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>设置上半身关节最大角度，joint_id=6，degree=-55.0</t>
+          <t>设置上半身关节最大角度：joint_id=6，degree=-45.0</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -30732,7 +30732,7 @@
         <v>6</v>
       </c>
       <c r="E28" t="n">
-        <v>-55</v>
+        <v>-45</v>
       </c>
       <c r="F28" t="n">
         <v>1</v>
@@ -30749,7 +30749,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>设置上半身关节最大角度，joint_id=6，degree=0.0</t>
+          <t>设置上半身关节最大角度：joint_id=6，degree=-15.0</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -30761,7 +30761,7 @@
         <v>6</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="F29" t="n">
         <v>1</v>
@@ -30778,7 +30778,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>设置上半身关节最大角度，joint_id=6，degree=10.0</t>
+          <t>设置上半身关节最大角度：joint_id=6，degree=15.0</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -30790,7 +30790,7 @@
         <v>6</v>
       </c>
       <c r="E30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F30" t="n">
         <v>1</v>
@@ -30807,7 +30807,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>设置上半身关节最大角度，joint_id=6，degree=42.0</t>
+          <t>设置上半身关节最大角度：joint_id=6，degree=45.0</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -30819,7 +30819,7 @@
         <v>6</v>
       </c>
       <c r="E31" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F31" t="n">
         <v>1</v>
@@ -30836,7 +30836,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>设置上半身关节最大角度，joint_id=7，degree=-80.0</t>
+          <t>设置上半身关节最大角度：joint_id=7，degree=-80.0</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -30865,7 +30865,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>设置上半身关节最大角度，joint_id=7，degree=-37.0</t>
+          <t>设置上半身关节最大角度：joint_id=7，degree=-41.2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -30877,7 +30877,7 @@
         <v>7</v>
       </c>
       <c r="E33" t="n">
-        <v>-37</v>
+        <v>-41.2</v>
       </c>
       <c r="F33" t="n">
         <v>1</v>
@@ -30894,7 +30894,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>设置上半身关节最大角度，joint_id=7，degree=0.0</t>
+          <t>设置上半身关节最大角度：joint_id=7，degree=-2.5</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -30906,7 +30906,7 @@
         <v>7</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>-2.5</v>
       </c>
       <c r="F34" t="n">
         <v>1</v>
@@ -30923,7 +30923,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>设置上半身关节最大角度，joint_id=7，degree=49.0</t>
+          <t>设置上半身关节最大角度：joint_id=7，degree=36.2</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -30935,7 +30935,7 @@
         <v>7</v>
       </c>
       <c r="E35" t="n">
-        <v>49</v>
+        <v>36.2</v>
       </c>
       <c r="F35" t="n">
         <v>1</v>
@@ -30952,7 +30952,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>设置上半身关节最大角度，joint_id=7，degree=92.0</t>
+          <t>设置上半身关节最大角度：joint_id=7，degree=75.0</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -30964,7 +30964,7 @@
         <v>7</v>
       </c>
       <c r="E36" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="F36" t="n">
         <v>1</v>
@@ -31090,7 +31090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA129"/>
+  <dimension ref="A1:AA127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31236,7 +31236,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>刷新模式设置左臂J1运动到10度（速度20）</t>
+          <t>刷新模式下左臂J1运动到10度，速度20</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -31281,7 +31281,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>刷新模式设置左臂J2运动到-20度（速度10）</t>
+          <t>刷新模式下左臂J2运动到-8度，速度10</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -31293,7 +31293,7 @@
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>-20</v>
+        <v>-8</v>
       </c>
       <c r="F3" t="n">
         <v>10</v>
@@ -31326,7 +31326,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>刷新模式设置左臂J3运动到20度（速度20）</t>
+          <t>刷新模式下左臂J3运动到-70度，速度20</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -31338,7 +31338,7 @@
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>20</v>
+        <v>-70</v>
       </c>
       <c r="F4" t="n">
         <v>20</v>
@@ -31371,7 +31371,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>刷新模式设置左臂J4运动到-30度（速度10）</t>
+          <t>刷新模式下左臂J4运动到-15度，速度10</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -31383,7 +31383,7 @@
         <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>-30</v>
+        <v>-15</v>
       </c>
       <c r="F5" t="n">
         <v>10</v>
@@ -31416,7 +31416,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>刷新模式设置左臂J5运动到20度（速度30）</t>
+          <t>刷新模式下左臂J5运动到110度，速度30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -31428,7 +31428,7 @@
         <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="F6" t="n">
         <v>30</v>
@@ -31461,7 +31461,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>刷新模式设置左臂J6运动到10度（速度20）</t>
+          <t>刷新模式下左臂J6运动到10度，速度20</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -31506,7 +31506,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>刷新模式设置左臂J7运动到20度（速度10）</t>
+          <t>刷新模式下左臂J7运动到20度，速度10</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -31551,7 +31551,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>插补模式设置左臂J1运动到10度（速度20）</t>
+          <t>插补模式下左臂J1运动到10度，速度20</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -31596,7 +31596,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>插补模式设置左臂J2运动到-20度（速度10）</t>
+          <t>插补模式下左臂J2运动到-8度，速度10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -31608,7 +31608,7 @@
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>-20</v>
+        <v>-8</v>
       </c>
       <c r="F10" t="n">
         <v>10</v>
@@ -31641,7 +31641,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>插补模式设置左臂J3运动到20度（速度20）</t>
+          <t>插补模式下左臂J3运动到-70度，速度20</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -31653,7 +31653,7 @@
         <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>20</v>
+        <v>-70</v>
       </c>
       <c r="F11" t="n">
         <v>20</v>
@@ -31686,7 +31686,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>插补模式设置左臂J4运动到-30度（速度10）</t>
+          <t>插补模式下左臂J4运动到-15度，速度10</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -31698,7 +31698,7 @@
         <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>-30</v>
+        <v>-15</v>
       </c>
       <c r="F12" t="n">
         <v>10</v>
@@ -31731,7 +31731,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>插补模式设置左臂J5运动到20度（速度30）</t>
+          <t>插补模式下左臂J5运动到110度，速度30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -31743,7 +31743,7 @@
         <v>5</v>
       </c>
       <c r="E13" t="n">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="F13" t="n">
         <v>30</v>
@@ -31776,7 +31776,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>插补模式设置左臂J6运动到10度（速度20）</t>
+          <t>插补模式下左臂J6运动到10度，速度20</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -31821,7 +31821,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>插补模式设置左臂J7运动到20度（速度10）</t>
+          <t>插补模式下左臂J7运动到20度，速度10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -31866,7 +31866,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>刷新模式设置右臂J1运动到10度（速度20）</t>
+          <t>刷新模式下右臂J1运动到10度，速度20</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -31911,7 +31911,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>刷新模式设置右臂J2运动到-20度（速度10）</t>
+          <t>刷新模式下右臂J2运动到-8度，速度10</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -31923,7 +31923,7 @@
         <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>-20</v>
+        <v>-8</v>
       </c>
       <c r="F17" t="n">
         <v>10</v>
@@ -31956,7 +31956,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>刷新模式设置右臂J3运动到20度（速度20）</t>
+          <t>刷新模式下右臂J3运动到110度，速度20</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -31968,7 +31968,7 @@
         <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="F18" t="n">
         <v>20</v>
@@ -32001,7 +32001,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>刷新模式设置右臂J4运动到-30度（速度10）</t>
+          <t>刷新模式下右臂J4运动到-15度，速度10</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -32013,7 +32013,7 @@
         <v>4</v>
       </c>
       <c r="E19" t="n">
-        <v>-30</v>
+        <v>-15</v>
       </c>
       <c r="F19" t="n">
         <v>10</v>
@@ -32046,7 +32046,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>刷新模式设置右臂J5运动到20度（速度30）</t>
+          <t>刷新模式下右臂J5运动到-70度，速度30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -32058,7 +32058,7 @@
         <v>5</v>
       </c>
       <c r="E20" t="n">
-        <v>20</v>
+        <v>-70</v>
       </c>
       <c r="F20" t="n">
         <v>30</v>
@@ -32091,7 +32091,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>刷新模式设置右臂J6运动到10度（速度20）</t>
+          <t>刷新模式下右臂J6运动到10度，速度20</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -32136,7 +32136,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>刷新模式设置右臂J7运动到20度（速度10）</t>
+          <t>刷新模式下右臂J7运动到20度，速度10</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -32181,7 +32181,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>插补模式设置右臂J1运动到10度（速度20）</t>
+          <t>插补模式下右臂J1运动到10度，速度20</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -32226,7 +32226,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>插补模式设置右臂J2运动到-20度（速度10）</t>
+          <t>插补模式下右臂J2运动到-8度，速度10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -32238,7 +32238,7 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>-20</v>
+        <v>-8</v>
       </c>
       <c r="F24" t="n">
         <v>10</v>
@@ -32271,7 +32271,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>插补模式设置右臂J3运动到20度（速度20）</t>
+          <t>插补模式下右臂J3运动到110度，速度20</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -32283,7 +32283,7 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="F25" t="n">
         <v>20</v>
@@ -32316,7 +32316,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>插补模式设置右臂J4运动到-30度（速度10）</t>
+          <t>插补模式下右臂J4运动到-15度，速度10</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -32328,7 +32328,7 @@
         <v>4</v>
       </c>
       <c r="E26" t="n">
-        <v>-30</v>
+        <v>-15</v>
       </c>
       <c r="F26" t="n">
         <v>10</v>
@@ -32361,7 +32361,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>插补模式设置右臂J5运动到20度（速度30）</t>
+          <t>插补模式下右臂J5运动到-70度，速度30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -32373,7 +32373,7 @@
         <v>5</v>
       </c>
       <c r="E27" t="n">
-        <v>20</v>
+        <v>-70</v>
       </c>
       <c r="F27" t="n">
         <v>30</v>
@@ -32406,7 +32406,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>插补模式设置右臂J6运动到10度（速度20）</t>
+          <t>插补模式下右臂J6运动到10度，速度20</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -32451,7 +32451,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>插补模式设置右臂J7运动到20度（速度10）</t>
+          <t>插补模式下右臂J7运动到20度，速度10</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -32496,7 +32496,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>刷新模式设置双臂J1同时运动到10度（速度10）</t>
+          <t>刷新模式下双臂J1同时运动到10度，速度10</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -32536,7 +32536,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>刷新模式设置双臂J1同时运动到-10度（速度10）</t>
+          <t>刷新模式下双臂J1同时运动到-10度，速度10</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -32576,7 +32576,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>刷新模式设置双臂J2同时运动到10度（速度10）</t>
+          <t>刷新模式下双臂J2同时运动到22度，速度10</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -32588,7 +32588,7 @@
         <v>2</v>
       </c>
       <c r="E32" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F32" t="n">
         <v>10</v>
@@ -32616,7 +32616,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>刷新模式设置双臂J2同时运动到-10度（速度10）</t>
+          <t>刷新模式下双臂J2同时运动到2度，速度10</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -32628,7 +32628,7 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>-10</v>
+        <v>2</v>
       </c>
       <c r="F33" t="n">
         <v>10</v>
@@ -32656,7 +32656,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>刷新模式设置双臂J3同时运动到10度（速度10）</t>
+          <t>刷新模式下双臂J3同时运动到10度，速度10</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -32696,7 +32696,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>刷新模式设置双臂J3同时运动到-10度（速度10）</t>
+          <t>刷新模式下双臂J3同时运动到-10度，速度10</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -32736,7 +32736,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>刷新模式设置双臂J4同时运动到1度（速度10）</t>
+          <t>刷新模式下双臂J4同时运动到-15度，速度10</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -32748,7 +32748,7 @@
         <v>4</v>
       </c>
       <c r="E36" t="n">
-        <v>1</v>
+        <v>-15</v>
       </c>
       <c r="F36" t="n">
         <v>10</v>
@@ -32776,7 +32776,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>刷新模式设置双臂J4同时运动到-10度（速度10）</t>
+          <t>刷新模式下双臂J5同时运动到10度，速度10</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -32785,10 +32785,10 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E37" t="n">
-        <v>-10</v>
+        <v>10</v>
       </c>
       <c r="F37" t="n">
         <v>10</v>
@@ -32816,7 +32816,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>刷新模式设置双臂J5同时运动到10度（速度10）</t>
+          <t>刷新模式下双臂J5同时运动到-10度，速度10</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -32828,7 +32828,7 @@
         <v>5</v>
       </c>
       <c r="E38" t="n">
-        <v>10</v>
+        <v>-10</v>
       </c>
       <c r="F38" t="n">
         <v>10</v>
@@ -32856,7 +32856,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>刷新模式设置双臂J5同时运动到-10度（速度10）</t>
+          <t>刷新模式下双臂J6同时运动到10度，速度10</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -32865,10 +32865,10 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E39" t="n">
-        <v>-10</v>
+        <v>10</v>
       </c>
       <c r="F39" t="n">
         <v>10</v>
@@ -32896,7 +32896,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>刷新模式设置双臂J6同时运动到10度（速度10）</t>
+          <t>刷新模式下双臂J6同时运动到-10度，速度10</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -32908,7 +32908,7 @@
         <v>6</v>
       </c>
       <c r="E40" t="n">
-        <v>10</v>
+        <v>-10</v>
       </c>
       <c r="F40" t="n">
         <v>10</v>
@@ -32936,7 +32936,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>刷新模式设置双臂J6同时运动到-10度（速度10）</t>
+          <t>刷新模式下双臂J7同时运动到10度，速度10</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -32945,10 +32945,10 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E41" t="n">
-        <v>-10</v>
+        <v>10</v>
       </c>
       <c r="F41" t="n">
         <v>10</v>
@@ -32976,7 +32976,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>刷新模式设置双臂J7同时运动到10度（速度10）</t>
+          <t>刷新模式下双臂J7同时运动到-10度，速度10</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -32988,7 +32988,7 @@
         <v>7</v>
       </c>
       <c r="E42" t="n">
-        <v>10</v>
+        <v>-10</v>
       </c>
       <c r="F42" t="n">
         <v>10</v>
@@ -33016,7 +33016,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>刷新模式设置双臂J7同时运动到-10度（速度10）</t>
+          <t>插补模式下双臂J1同时运动到10度，速度10</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -33025,16 +33025,16 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>-10</v>
+        <v>10</v>
       </c>
       <c r="F43" t="n">
         <v>10</v>
       </c>
       <c r="G43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -33047,7 +33047,7 @@
         </is>
       </c>
       <c r="AA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -33056,7 +33056,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>插补模式设置双臂J1同时运动到10度（速度10）</t>
+          <t>插补模式下双臂J1同时运动到-10度，速度10</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -33068,7 +33068,7 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>10</v>
+        <v>-10</v>
       </c>
       <c r="F44" t="n">
         <v>10</v>
@@ -33096,7 +33096,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>插补模式设置双臂J1同时运动到-10度（速度10）</t>
+          <t>插补模式下双臂J2同时运动到22度，速度10</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -33105,10 +33105,10 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>-10</v>
+        <v>22</v>
       </c>
       <c r="F45" t="n">
         <v>10</v>
@@ -33136,7 +33136,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>插补模式设置双臂J2同时运动到10度（速度10）</t>
+          <t>插补模式下双臂J2同时运动到2度，速度10</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -33148,7 +33148,7 @@
         <v>2</v>
       </c>
       <c r="E46" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F46" t="n">
         <v>10</v>
@@ -33176,7 +33176,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>插补模式设置双臂J2同时运动到-10度（速度10）</t>
+          <t>插补模式下双臂J3同时运动到10度，速度10</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -33185,10 +33185,10 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E47" t="n">
-        <v>-10</v>
+        <v>10</v>
       </c>
       <c r="F47" t="n">
         <v>10</v>
@@ -33216,7 +33216,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>插补模式设置双臂J3同时运动到10度（速度10）</t>
+          <t>插补模式下双臂J3同时运动到-10度，速度10</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -33228,7 +33228,7 @@
         <v>3</v>
       </c>
       <c r="E48" t="n">
-        <v>10</v>
+        <v>-10</v>
       </c>
       <c r="F48" t="n">
         <v>10</v>
@@ -33256,7 +33256,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>插补模式设置双臂J3同时运动到-10度（速度10）</t>
+          <t>插补模式下双臂J4同时运动到-15度，速度10</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -33265,10 +33265,10 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E49" t="n">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="F49" t="n">
         <v>10</v>
@@ -33296,7 +33296,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>插补模式设置双臂J4同时运动到1度（速度10）</t>
+          <t>插补模式下双臂J5同时运动到10度，速度10</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -33305,10 +33305,10 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E50" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F50" t="n">
         <v>10</v>
@@ -33336,7 +33336,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>插补模式设置双臂J4同时运动到-10度（速度10）</t>
+          <t>插补模式下双臂J5同时运动到-10度，速度10</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -33345,7 +33345,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E51" t="n">
         <v>-10</v>
@@ -33376,7 +33376,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>插补模式设置双臂J5同时运动到10度（速度10）</t>
+          <t>插补模式下双臂J6同时运动到10度，速度10</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -33385,7 +33385,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E52" t="n">
         <v>10</v>
@@ -33416,7 +33416,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>插补模式设置双臂J5同时运动到-10度（速度10）</t>
+          <t>插补模式下双臂J6同时运动到-10度，速度10</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -33425,7 +33425,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E53" t="n">
         <v>-10</v>
@@ -33456,7 +33456,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>插补模式设置双臂J6同时运动到10度（速度10）</t>
+          <t>插补模式下双臂J7同时运动到10度，速度10</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -33465,7 +33465,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E54" t="n">
         <v>10</v>
@@ -33496,7 +33496,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>插补模式设置双臂J6同时运动到-10度（速度10）</t>
+          <t>插补模式下双臂J7同时运动到-10度，速度10</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -33505,7 +33505,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E55" t="n">
         <v>-10</v>
@@ -33536,7 +33536,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>插补模式设置双臂J7同时运动到10度（速度10）</t>
+          <t>设置J7运动速度为0，验证速度超限</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -33548,26 +33548,20 @@
         <v>7</v>
       </c>
       <c r="E56" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>10</v>
-      </c>
-      <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>exception</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
           <t>dual</t>
         </is>
-      </c>
-      <c r="AA56" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -33576,7 +33570,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>插补模式设置双臂J7同时运动到-10度（速度10）</t>
+          <t>设置J7运动速度为101，验证速度超限</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -33588,26 +33582,20 @@
         <v>7</v>
       </c>
       <c r="E57" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>10</v>
-      </c>
-      <c r="G57" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>exception</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
           <t>dual</t>
         </is>
-      </c>
-      <c r="AA57" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -33616,7 +33604,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>设置J7运动速度为0，验证速度超限</t>
+          <t>设置J1运动到-151度，验证角度超限</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -33625,13 +33613,13 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>-151</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -33650,7 +33638,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>设置J7运动速度为101，验证速度超限</t>
+          <t>设置J1运动到177度，验证角度超限</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -33659,13 +33647,13 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>0</v>
+        <v>177</v>
       </c>
       <c r="F59" t="n">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -33684,7 +33672,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>设置J1运动到-151度，验证角度超限</t>
+          <t>设置J2运动到-66度，验证角度超限</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -33693,10 +33681,10 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>-151</v>
+        <v>-66</v>
       </c>
       <c r="F60" t="n">
         <v>10</v>
@@ -33718,7 +33706,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>设置J1运动到177度，验证角度超限</t>
+          <t>设置J2运动到111度，验证角度超限</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -33727,10 +33715,10 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E61" t="n">
-        <v>177</v>
+        <v>111</v>
       </c>
       <c r="F61" t="n">
         <v>10</v>
@@ -33752,7 +33740,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>设置J2运动到-73度，验证角度超限</t>
+          <t>设置J3运动到-166度，验证角度超限</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -33761,10 +33749,10 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E62" t="n">
-        <v>-73</v>
+        <v>-166</v>
       </c>
       <c r="F62" t="n">
         <v>10</v>
@@ -33786,7 +33774,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>设置J2运动到126度，验证角度超限</t>
+          <t>设置J3运动到166度，验证角度超限</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -33795,10 +33783,10 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E63" t="n">
-        <v>126</v>
+        <v>166</v>
       </c>
       <c r="F63" t="n">
         <v>10</v>
@@ -33820,7 +33808,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>设置J3运动到-164度，验证角度超限</t>
+          <t>设置J4运动到-165度，验证角度超限</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -33829,10 +33817,10 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E64" t="n">
-        <v>-164</v>
+        <v>-165</v>
       </c>
       <c r="F64" t="n">
         <v>10</v>
@@ -33854,7 +33842,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>设置J3运动到168度，验证角度超限</t>
+          <t>设置J4运动到-9度，验证角度超限</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -33863,10 +33851,10 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E65" t="n">
-        <v>168</v>
+        <v>-9</v>
       </c>
       <c r="F65" t="n">
         <v>10</v>
@@ -33888,7 +33876,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>设置J4运动到-150度，验证角度超限</t>
+          <t>设置J5运动到-166度，验证角度超限</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -33897,10 +33885,10 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E66" t="n">
-        <v>-150</v>
+        <v>-166</v>
       </c>
       <c r="F66" t="n">
         <v>10</v>
@@ -33922,7 +33910,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>设置J4运动到2度，验证角度超限</t>
+          <t>设置J5运动到166度，验证角度超限</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -33931,10 +33919,10 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E67" t="n">
-        <v>2</v>
+        <v>166</v>
       </c>
       <c r="F67" t="n">
         <v>10</v>
@@ -33956,7 +33944,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>设置J5运动到-180度，验证角度超限</t>
+          <t>设置J6运动到-76度，验证角度超限</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -33965,10 +33953,10 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E68" t="n">
-        <v>-180</v>
+        <v>-76</v>
       </c>
       <c r="F68" t="n">
         <v>10</v>
@@ -33990,7 +33978,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>设置J5运动到149度，验证角度超限</t>
+          <t>设置J6运动到46度，验证角度超限</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -33999,10 +33987,10 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E69" t="n">
-        <v>149</v>
+        <v>46</v>
       </c>
       <c r="F69" t="n">
         <v>10</v>
@@ -34024,7 +34012,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>设置J6运动到-88度，验证角度超限</t>
+          <t>设置J7运动到-81度，验证角度超限</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -34033,10 +34021,10 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E70" t="n">
-        <v>-88</v>
+        <v>-81</v>
       </c>
       <c r="F70" t="n">
         <v>10</v>
@@ -34058,7 +34046,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>设置J6运动到43度，验证角度超限</t>
+          <t>设置J7运动到76度，验证角度超限</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -34067,10 +34055,10 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E71" t="n">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="F71" t="n">
         <v>10</v>
@@ -34092,7 +34080,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>设置J7运动到-81度，验证角度超限</t>
+          <t>刷新模式下设置左臂J1运动到-150度，验证软件限位运动，速度10</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -34101,23 +34089,34 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E72" t="n">
-        <v>-81</v>
+        <v>-150</v>
       </c>
       <c r="F72" t="n">
         <v>10</v>
       </c>
+      <c r="G72" t="n">
+        <v>1</v>
+      </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>exception</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>dual</t>
-        </is>
+          <t>separate</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="AA72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -34126,7 +34125,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>设置J7运动到93度，验证角度超限</t>
+          <t>刷新模式下设置左臂J1运动到176度，验证软件限位运动，速度20</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -34135,23 +34134,34 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E73" t="n">
-        <v>93</v>
+        <v>176</v>
       </c>
       <c r="F73" t="n">
-        <v>10</v>
+        <v>20</v>
+      </c>
+      <c r="G73" t="n">
+        <v>1</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>exception</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>dual</t>
-        </is>
+          <t>separate</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="AA73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -34160,7 +34170,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>刷新模式下设置左臂J1运动到-150度，验证软件限位运动，速度10度</t>
+          <t>刷新模式下设置左臂J2运动到-65度，验证软件限位运动，速度30</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -34169,13 +34179,13 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E74" t="n">
-        <v>-150</v>
+        <v>-65</v>
       </c>
       <c r="F74" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G74" t="n">
         <v>1</v>
@@ -34205,7 +34215,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>刷新模式下设置左臂J1运动到176度，验证软件限位运动，速度20度</t>
+          <t>刷新模式下设置左臂J2运动到110度，验证软件限位运动，速度20</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -34214,10 +34224,10 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>176</v>
+        <v>110</v>
       </c>
       <c r="F75" t="n">
         <v>20</v>
@@ -34250,7 +34260,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>刷新模式下设置左臂J2运动到-72度，验证软件限位运动，速度30度</t>
+          <t>刷新模式下设置左臂J3运动到-165度，验证软件限位运动，速度40</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -34259,13 +34269,13 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>-72</v>
+        <v>-165</v>
       </c>
       <c r="F76" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G76" t="n">
         <v>1</v>
@@ -34295,7 +34305,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>刷新模式下设置左臂J2运动到125度，验证软件限位运动，速度20度</t>
+          <t>刷新模式下设置左臂J3运动到165度，验证软件限位运动，速度30</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -34304,13 +34314,13 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E77" t="n">
-        <v>125</v>
+        <v>165</v>
       </c>
       <c r="F77" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G77" t="n">
         <v>1</v>
@@ -34340,7 +34350,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>刷新模式下设置左臂J3运动到-163度，验证软件限位运动，速度40度</t>
+          <t>刷新模式下设置左臂J4运动到-164度，验证软件限位运动，速度30</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -34349,13 +34359,13 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E78" t="n">
-        <v>-163</v>
+        <v>-164</v>
       </c>
       <c r="F78" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G78" t="n">
         <v>1</v>
@@ -34385,7 +34395,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>刷新模式下设置左臂J3运动到167度，验证软件限位运动，速度30度</t>
+          <t>刷新模式下设置左臂J4运动到-10度，验证软件限位运动，速度50</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -34394,13 +34404,13 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E79" t="n">
-        <v>167</v>
+        <v>-10</v>
       </c>
       <c r="F79" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G79" t="n">
         <v>1</v>
@@ -34430,7 +34440,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>刷新模式下设置左臂J4运动到-149度，验证软件限位运动，速度30度</t>
+          <t>刷新模式下设置左臂J5运动到-165度，验证软件限位运动，速度20</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -34439,13 +34449,13 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E80" t="n">
-        <v>-149</v>
+        <v>-165</v>
       </c>
       <c r="F80" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G80" t="n">
         <v>1</v>
@@ -34475,7 +34485,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>刷新模式下设置左臂J4运动到1度，验证软件限位运动，速度50度</t>
+          <t>刷新模式下设置左臂J5运动到165度，验证软件限位运动，速度20</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -34484,13 +34494,13 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E81" t="n">
-        <v>1</v>
+        <v>165</v>
       </c>
       <c r="F81" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="G81" t="n">
         <v>1</v>
@@ -34520,7 +34530,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>刷新模式下设置左臂J5运动到-179度，验证软件限位运动，速度20度</t>
+          <t>刷新模式下设置左臂J6运动到-75度，验证软件限位运动，速度40</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -34529,13 +34539,13 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E82" t="n">
-        <v>-179</v>
+        <v>-75</v>
       </c>
       <c r="F82" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="G82" t="n">
         <v>1</v>
@@ -34565,7 +34575,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>刷新模式下设置左臂J5运动到148度，验证软件限位运动，速度20度</t>
+          <t>刷新模式下设置左臂J6运动到45度，验证软件限位运动，速度60</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -34574,13 +34584,13 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E83" t="n">
-        <v>148</v>
+        <v>45</v>
       </c>
       <c r="F83" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="G83" t="n">
         <v>1</v>
@@ -34610,7 +34620,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>刷新模式下设置左臂J6运动到-87度，验证软件限位运动，速度40度</t>
+          <t>刷新模式下设置左臂J7运动到-80度，验证软件限位运动，速度100</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -34619,13 +34629,13 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E84" t="n">
-        <v>-87</v>
+        <v>-80</v>
       </c>
       <c r="F84" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="G84" t="n">
         <v>1</v>
@@ -34655,7 +34665,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>刷新模式下设置左臂J6运动到42度，验证软件限位运动，速度60度</t>
+          <t>刷新模式下设置左臂J7运动到75度，验证软件限位运动，速度90</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -34664,13 +34674,13 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E85" t="n">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="F85" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="G85" t="n">
         <v>1</v>
@@ -34700,7 +34710,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>刷新模式下设置左臂J7运动到-80度，验证软件限位运动，速度100度</t>
+          <t>插补模式下设置左臂J1运动到-150度，验证软件限位运动，速度10</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -34709,16 +34719,16 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>-80</v>
+        <v>-150</v>
       </c>
       <c r="F86" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="G86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -34736,7 +34746,7 @@
         </is>
       </c>
       <c r="AA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -34745,7 +34755,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>刷新模式下设置左臂J7运动到92度，验证软件限位运动，速度90度</t>
+          <t>插补模式下设置左臂J1运动到176度，验证软件限位运动，速度20</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -34754,16 +34764,16 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E87" t="n">
-        <v>92</v>
+        <v>176</v>
       </c>
       <c r="F87" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="G87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -34781,7 +34791,7 @@
         </is>
       </c>
       <c r="AA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -34790,7 +34800,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>插补模式下设置左臂J1运动到-150度，验证软件限位运动，速度10度</t>
+          <t>插补模式下设置左臂J2运动到-65度，验证软件限位运动，速度30</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -34799,13 +34809,13 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E88" t="n">
-        <v>-150</v>
+        <v>-65</v>
       </c>
       <c r="F88" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -34835,7 +34845,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>插补模式下设置左臂J1运动到176度，验证软件限位运动，速度20度</t>
+          <t>插补模式下设置左臂J2运动到110度，验证软件限位运动，速度20</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -34844,10 +34854,10 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E89" t="n">
-        <v>176</v>
+        <v>110</v>
       </c>
       <c r="F89" t="n">
         <v>20</v>
@@ -34880,7 +34890,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>插补模式下设置左臂J2运动到-72度，验证软件限位运动，速度30度</t>
+          <t>插补模式下设置左臂J3运动到-165度，验证软件限位运动，速度40</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -34889,13 +34899,13 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E90" t="n">
-        <v>-72</v>
+        <v>-165</v>
       </c>
       <c r="F90" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -34925,7 +34935,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>插补模式下设置左臂J2运动到125度，验证软件限位运动，速度20度</t>
+          <t>插补模式下设置左臂J3运动到165度，验证软件限位运动，速度30</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -34934,13 +34944,13 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E91" t="n">
-        <v>125</v>
+        <v>165</v>
       </c>
       <c r="F91" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -34970,7 +34980,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>插补模式下设置左臂J3运动到-163度，验证软件限位运动，速度40度</t>
+          <t>插补模式下设置左臂J4运动到-164度，验证软件限位运动，速度30</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -34979,13 +34989,13 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E92" t="n">
-        <v>-163</v>
+        <v>-164</v>
       </c>
       <c r="F92" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -35015,7 +35025,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>插补模式下设置左臂J3运动到167度，验证软件限位运动，速度30度</t>
+          <t>插补模式下设置左臂J4运动到-10度，验证软件限位运动，速度50</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -35024,13 +35034,13 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E93" t="n">
-        <v>167</v>
+        <v>-10</v>
       </c>
       <c r="F93" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -35060,7 +35070,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>插补模式下设置左臂J4运动到-149度，验证软件限位运动，速度30度</t>
+          <t>插补模式下设置左臂J5运动到-165度，验证软件限位运动，速度20</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -35069,13 +35079,13 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E94" t="n">
-        <v>-149</v>
+        <v>-165</v>
       </c>
       <c r="F94" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -35105,7 +35115,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>插补模式下设置左臂J4运动到1度，验证软件限位运动，速度50度</t>
+          <t>插补模式下设置左臂J5运动到165度，验证软件限位运动，速度20</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -35114,13 +35124,13 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E95" t="n">
-        <v>1</v>
+        <v>165</v>
       </c>
       <c r="F95" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -35150,7 +35160,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>插补模式下设置左臂J5运动到-179度，验证软件限位运动，速度20度</t>
+          <t>插补模式下设置左臂J6运动到-75度，验证软件限位运动，速度40</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -35159,13 +35169,13 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E96" t="n">
-        <v>-179</v>
+        <v>-75</v>
       </c>
       <c r="F96" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -35195,7 +35205,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>插补模式下设置左臂J5运动到148度，验证软件限位运动，速度20度</t>
+          <t>插补模式下设置左臂J6运动到45度，验证软件限位运动，速度60</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -35204,13 +35214,13 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E97" t="n">
-        <v>148</v>
+        <v>45</v>
       </c>
       <c r="F97" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -35240,7 +35250,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>插补模式下设置左臂J6运动到-87度，验证软件限位运动，速度40度</t>
+          <t>插补模式下设置左臂J7运动到-80度，验证软件限位运动，速度100</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -35249,13 +35259,13 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E98" t="n">
-        <v>-87</v>
+        <v>-80</v>
       </c>
       <c r="F98" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -35285,7 +35295,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>插补模式下设置左臂J6运动到42度，验证软件限位运动，速度60度</t>
+          <t>插补模式下设置左臂J7运动到75度，验证软件限位运动，速度90</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -35294,13 +35304,13 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E99" t="n">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="F99" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -35330,7 +35340,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>插补模式下设置左臂J7运动到-80度，验证软件限位运动，速度100度</t>
+          <t>刷新模式下设置右臂J1运动到-150度，验证软件限位运动，速度10</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -35339,16 +35349,16 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E100" t="n">
-        <v>-80</v>
+        <v>-150</v>
       </c>
       <c r="F100" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="G100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -35362,11 +35372,11 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
@@ -35375,7 +35385,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>插补模式下设置左臂J7运动到92度，验证软件限位运动，速度90度</t>
+          <t>刷新模式下设置右臂J1运动到176度，验证软件限位运动，速度20</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -35384,16 +35394,16 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E101" t="n">
-        <v>92</v>
+        <v>176</v>
       </c>
       <c r="F101" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -35407,11 +35417,11 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="AA101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
@@ -35420,7 +35430,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>刷新模式下设置右臂J1运动到-150度，验证软件限位运动，速度10度</t>
+          <t>刷新模式下设置右臂J2运动到-65度，验证软件限位运动，速度30</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -35429,13 +35439,13 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E102" t="n">
-        <v>-150</v>
+        <v>-65</v>
       </c>
       <c r="F102" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G102" t="n">
         <v>1</v>
@@ -35465,7 +35475,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>刷新模式下设置右臂J1运动到176度，验证软件限位运动，速度20度</t>
+          <t>刷新模式下设置右臂J2运动到110度，验证软件限位运动，速度20</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -35474,10 +35484,10 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E103" t="n">
-        <v>176</v>
+        <v>110</v>
       </c>
       <c r="F103" t="n">
         <v>20</v>
@@ -35510,7 +35520,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>刷新模式下设置右臂J2运动到-72度，验证软件限位运动，速度30度</t>
+          <t>刷新模式下设置右臂J3运动到-165度，验证软件限位运动，速度40</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -35519,13 +35529,13 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E104" t="n">
-        <v>-72</v>
+        <v>-165</v>
       </c>
       <c r="F104" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G104" t="n">
         <v>1</v>
@@ -35555,7 +35565,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>刷新模式下设置右臂J2运动到125度，验证软件限位运动，速度20度</t>
+          <t>刷新模式下设置右臂J3运动到165度，验证软件限位运动，速度30</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -35564,13 +35574,13 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E105" t="n">
-        <v>125</v>
+        <v>165</v>
       </c>
       <c r="F105" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G105" t="n">
         <v>1</v>
@@ -35600,7 +35610,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>刷新模式下设置右臂J3运动到-163度，验证软件限位运动，速度40度</t>
+          <t>刷新模式下设置右臂J4运动到-164度，验证软件限位运动，速度30</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -35609,13 +35619,13 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E106" t="n">
-        <v>-163</v>
+        <v>-164</v>
       </c>
       <c r="F106" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G106" t="n">
         <v>1</v>
@@ -35645,7 +35655,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>刷新模式下设置右臂J3运动到167度，验证软件限位运动，速度30度</t>
+          <t>刷新模式下设置右臂J4运动到-10度，验证软件限位运动，速度50</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -35654,13 +35664,13 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E107" t="n">
-        <v>167</v>
+        <v>-10</v>
       </c>
       <c r="F107" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G107" t="n">
         <v>1</v>
@@ -35690,7 +35700,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>刷新模式下设置右臂J4运动到-149度，验证软件限位运动，速度30度</t>
+          <t>刷新模式下设置右臂J5运动到-165度，验证软件限位运动，速度20</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -35699,13 +35709,13 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E108" t="n">
-        <v>-149</v>
+        <v>-165</v>
       </c>
       <c r="F108" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G108" t="n">
         <v>1</v>
@@ -35735,7 +35745,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>刷新模式下设置右臂J4运动到1度，验证软件限位运动，速度50度</t>
+          <t>刷新模式下设置右臂J5运动到165度，验证软件限位运动，速度20</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -35744,13 +35754,13 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E109" t="n">
-        <v>1</v>
+        <v>165</v>
       </c>
       <c r="F109" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="G109" t="n">
         <v>1</v>
@@ -35780,7 +35790,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>刷新模式下设置右臂J5运动到-179度，验证软件限位运动，速度20度</t>
+          <t>刷新模式下设置右臂J6运动到-75度，验证软件限位运动，速度40</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -35789,13 +35799,13 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E110" t="n">
-        <v>-179</v>
+        <v>-75</v>
       </c>
       <c r="F110" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="G110" t="n">
         <v>1</v>
@@ -35825,7 +35835,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>刷新模式下设置右臂J5运动到148度，验证软件限位运动，速度20度</t>
+          <t>刷新模式下设置右臂J6运动到45度，验证软件限位运动，速度60</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -35834,13 +35844,13 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E111" t="n">
-        <v>148</v>
+        <v>45</v>
       </c>
       <c r="F111" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="G111" t="n">
         <v>1</v>
@@ -35870,7 +35880,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>刷新模式下设置右臂J6运动到-87度，验证软件限位运动，速度40度</t>
+          <t>刷新模式下设置右臂J7运动到-80度，验证软件限位运动，速度100</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -35879,13 +35889,13 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E112" t="n">
-        <v>-87</v>
+        <v>-80</v>
       </c>
       <c r="F112" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="G112" t="n">
         <v>1</v>
@@ -35915,7 +35925,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>刷新模式下设置右臂J6运动到42度，验证软件限位运动，速度60度</t>
+          <t>刷新模式下设置右臂J7运动到75度，验证软件限位运动，速度90</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -35924,13 +35934,13 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E113" t="n">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="F113" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="G113" t="n">
         <v>1</v>
@@ -35960,7 +35970,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>刷新模式下设置右臂J7运动到-80度，验证软件限位运动，速度100度</t>
+          <t>插补模式下设置右臂J1运动到-150度，验证软件限位运动，速度10</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -35969,16 +35979,16 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E114" t="n">
-        <v>-80</v>
+        <v>-150</v>
       </c>
       <c r="F114" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="G114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -35996,7 +36006,7 @@
         </is>
       </c>
       <c r="AA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -36005,7 +36015,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>刷新模式下设置右臂J7运动到92度，验证软件限位运动，速度90度</t>
+          <t>插补模式下设置右臂J1运动到176度，验证软件限位运动，速度20</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -36014,16 +36024,16 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E115" t="n">
-        <v>92</v>
+        <v>176</v>
       </c>
       <c r="F115" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="G115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -36041,7 +36051,7 @@
         </is>
       </c>
       <c r="AA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -36050,7 +36060,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>插补模式下设置右臂J1运动到-150度，验证软件限位运动，速度10度</t>
+          <t>插补模式下设置右臂J2运动到-65度，验证软件限位运动，速度30</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -36059,13 +36069,13 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E116" t="n">
-        <v>-150</v>
+        <v>-65</v>
       </c>
       <c r="F116" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -36095,7 +36105,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>插补模式下设置右臂J1运动到176度，验证软件限位运动，速度20度</t>
+          <t>插补模式下设置右臂J2运动到110度，验证软件限位运动，速度20</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -36104,10 +36114,10 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E117" t="n">
-        <v>176</v>
+        <v>110</v>
       </c>
       <c r="F117" t="n">
         <v>20</v>
@@ -36140,7 +36150,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>插补模式下设置右臂J2运动到-72度，验证软件限位运动，速度30度</t>
+          <t>插补模式下设置右臂J3运动到-165度，验证软件限位运动，速度40</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -36149,13 +36159,13 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E118" t="n">
-        <v>-72</v>
+        <v>-165</v>
       </c>
       <c r="F118" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -36185,7 +36195,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>插补模式下设置右臂J2运动到125度，验证软件限位运动，速度20度</t>
+          <t>插补模式下设置右臂J3运动到165度，验证软件限位运动，速度30</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -36194,13 +36204,13 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E119" t="n">
-        <v>125</v>
+        <v>165</v>
       </c>
       <c r="F119" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -36230,7 +36240,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>插补模式下设置右臂J3运动到-163度，验证软件限位运动，速度40度</t>
+          <t>插补模式下设置右臂J4运动到-164度，验证软件限位运动，速度30</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -36239,13 +36249,13 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E120" t="n">
-        <v>-163</v>
+        <v>-164</v>
       </c>
       <c r="F120" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -36275,7 +36285,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>插补模式下设置右臂J3运动到167度，验证软件限位运动，速度30度</t>
+          <t>插补模式下设置右臂J4运动到-10度，验证软件限位运动，速度50</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -36284,13 +36294,13 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E121" t="n">
-        <v>167</v>
+        <v>-10</v>
       </c>
       <c r="F121" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -36320,7 +36330,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>插补模式下设置右臂J4运动到-149度，验证软件限位运动，速度30度</t>
+          <t>插补模式下设置右臂J5运动到-165度，验证软件限位运动，速度20</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -36329,13 +36339,13 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E122" t="n">
-        <v>-149</v>
+        <v>-165</v>
       </c>
       <c r="F122" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -36365,7 +36375,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>插补模式下设置右臂J4运动到1度，验证软件限位运动，速度50度</t>
+          <t>插补模式下设置右臂J5运动到165度，验证软件限位运动，速度20</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -36374,13 +36384,13 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E123" t="n">
-        <v>1</v>
+        <v>165</v>
       </c>
       <c r="F123" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -36410,7 +36420,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>插补模式下设置右臂J5运动到-179度，验证软件限位运动，速度20度</t>
+          <t>插补模式下设置右臂J6运动到-75度，验证软件限位运动，速度40</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -36419,13 +36429,13 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E124" t="n">
-        <v>-179</v>
+        <v>-75</v>
       </c>
       <c r="F124" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -36455,7 +36465,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>插补模式下设置右臂J5运动到148度，验证软件限位运动，速度20度</t>
+          <t>插补模式下设置右臂J6运动到45度，验证软件限位运动，速度60</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -36464,13 +36474,13 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E125" t="n">
-        <v>148</v>
+        <v>45</v>
       </c>
       <c r="F125" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -36500,7 +36510,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>插补模式下设置右臂J6运动到-87度，验证软件限位运动，速度40度</t>
+          <t>插补模式下设置右臂J7运动到-80度，验证软件限位运动，速度100</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -36509,13 +36519,13 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E126" t="n">
-        <v>-87</v>
+        <v>-80</v>
       </c>
       <c r="F126" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -36545,7 +36555,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>插补模式下设置右臂J6运动到42度，验证软件限位运动，速度60度</t>
+          <t>插补模式下设置右臂J7运动到75度，验证软件限位运动，速度90</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -36554,13 +36564,13 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E127" t="n">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="F127" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -36581,96 +36591,6 @@
         </is>
       </c>
       <c r="AA127" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="n">
-        <v>127</v>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>插补模式下设置右臂J7运动到-80度，验证软件限位运动，速度100度</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>send_upper_angle</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>7</v>
-      </c>
-      <c r="E128" t="n">
-        <v>-80</v>
-      </c>
-      <c r="F128" t="n">
-        <v>100</v>
-      </c>
-      <c r="G128" t="n">
-        <v>0</v>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="Y128" t="inlineStr">
-        <is>
-          <t>separate</t>
-        </is>
-      </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="AA128" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="n">
-        <v>128</v>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>插补模式下设置右臂J7运动到92度，验证软件限位运动，速度90度</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>send_upper_angle</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>7</v>
-      </c>
-      <c r="E129" t="n">
-        <v>92</v>
-      </c>
-      <c r="F129" t="n">
-        <v>90</v>
-      </c>
-      <c r="G129" t="n">
-        <v>0</v>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="Y129" t="inlineStr">
-        <is>
-          <t>separate</t>
-        </is>
-      </c>
-      <c r="Z129" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="AA129" t="n">
         <v>0</v>
       </c>
     </row>
@@ -36788,7 +36708,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>左臂J2以速度10步进30度后回零</t>
+          <t>左臂J2以速度20步进30度后回零</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -36825,7 +36745,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>左臂J3以速度10步进30度后回零</t>
+          <t>左臂J3以速度30步进30度后回零</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -36862,7 +36782,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>左臂J4以速度10步进-30度后回零</t>
+          <t>左臂J4以速度40步进-5度后回零</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -36879,7 +36799,7 @@
         <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>-30</v>
+        <v>-5</v>
       </c>
       <c r="G5" t="n">
         <v>40</v>
@@ -36899,7 +36819,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>左臂J5以速度10步进30度后回零</t>
+          <t>左臂J5以速度50步进30度后回零</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -36936,7 +36856,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>左臂J6以速度10步进30度后回零</t>
+          <t>左臂J6以速度20步进30度后回零</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -36973,7 +36893,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>左臂J7以速度10步进30度后回零</t>
+          <t>左臂J7以速度40步进30度后回零</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -37010,7 +36930,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>右臂J1以速度10步进30度后回零</t>
+          <t>右臂J1以速度70步进30度后回零</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -37047,7 +36967,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>右臂J2以速度10步进30度后回零</t>
+          <t>右臂J2以速度80步进30度后回零</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -37084,7 +37004,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>右臂J3以速度10步进30度后回零</t>
+          <t>右臂J3以速度20步进30度后回零</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -37121,7 +37041,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>右臂J4以速度10步进-30度后回零</t>
+          <t>右臂J4以速度90步进-5度后回零</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -37138,7 +37058,7 @@
         <v>4</v>
       </c>
       <c r="F12" t="n">
-        <v>-30</v>
+        <v>-5</v>
       </c>
       <c r="G12" t="n">
         <v>90</v>
@@ -37158,7 +37078,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>右臂J5以速度10步进30度后回零</t>
+          <t>右臂J5以速度100步进30度后回零</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -37195,7 +37115,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>右臂J6以速度10步进30度后回零</t>
+          <t>右臂J6以速度50步进30度后回零</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -37232,7 +37152,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>右臂J7以速度10步进30度后回零</t>
+          <t>右臂J7以速度60步进30度后回零</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -37269,7 +37189,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>双臂J1以速度10步进30度后回零</t>
+          <t>双臂J1以速度70步进30度后回零</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -37306,7 +37226,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>双臂J2以速度10步进30度后回零</t>
+          <t>双臂J2以速度80步进30度后回零</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -37380,7 +37300,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>双臂J4以速度10步进-30度后回零</t>
+          <t>双臂J4以速度20步进-5度后回零</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -37397,7 +37317,7 @@
         <v>4</v>
       </c>
       <c r="F19" t="n">
-        <v>-30</v>
+        <v>-5</v>
       </c>
       <c r="G19" t="n">
         <v>20</v>
@@ -37417,7 +37337,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>双臂J5以速度10步进30度后回零</t>
+          <t>双臂J5以速度1步进30度后回零</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -37454,7 +37374,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>双臂J6以速度10步进30度后回零</t>
+          <t>双臂J6以速度20步进30度后回零</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -37491,7 +37411,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>双臂J7以速度10步进30度后回零</t>
+          <t>双臂J7以速度50步进30度后回零</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -37528,7 +37448,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>左臂J1步进-327度，验证超限完整行程326度</t>
+          <t>左臂J1步进-328度，验证超出软件行程327度</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -37545,13 +37465,13 @@
         <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>-327</v>
+        <v>-328</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
       </c>
       <c r="H23" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -37565,7 +37485,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>左臂J1步进327度，验证超限完整行程326度</t>
+          <t>左臂J1步进328度，验证超出软件行程327度</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -37582,13 +37502,13 @@
         <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G24" t="n">
         <v>80</v>
       </c>
       <c r="H24" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -37602,7 +37522,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>左臂J2步进-198度，验证超限完整行程197度</t>
+          <t>左臂J2步进-177度，验证超出软件行程176度</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -37619,13 +37539,13 @@
         <v>2</v>
       </c>
       <c r="F25" t="n">
-        <v>-198</v>
+        <v>-177</v>
       </c>
       <c r="G25" t="n">
         <v>40</v>
       </c>
       <c r="H25" t="n">
-        <v>197</v>
+        <v>176</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -37639,7 +37559,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>左臂J2步进198度，验证超限完整行程197度</t>
+          <t>左臂J2步进177度，验证超出软件行程176度</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -37656,13 +37576,13 @@
         <v>2</v>
       </c>
       <c r="F26" t="n">
-        <v>198</v>
+        <v>177</v>
       </c>
       <c r="G26" t="n">
         <v>30</v>
       </c>
       <c r="H26" t="n">
-        <v>197</v>
+        <v>176</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -37676,7 +37596,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>左臂J3步进-331度，验证超限完整行程330度</t>
+          <t>左臂J3步进-332度，验证超出软件行程331度</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -37693,13 +37613,13 @@
         <v>3</v>
       </c>
       <c r="F27" t="n">
-        <v>-331</v>
+        <v>-332</v>
       </c>
       <c r="G27" t="n">
         <v>20</v>
       </c>
       <c r="H27" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -37713,7 +37633,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>左臂J3步进331度，验证超限完整行程330度</t>
+          <t>左臂J3步进332度，验证超出软件行程331度</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -37730,13 +37650,13 @@
         <v>3</v>
       </c>
       <c r="F28" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G28" t="n">
         <v>10</v>
       </c>
       <c r="H28" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -37750,7 +37670,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>左臂J4步进-151度，验证超限完整行程150度</t>
+          <t>左臂J4步进-176度，验证超出软件行程175度</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -37767,13 +37687,13 @@
         <v>4</v>
       </c>
       <c r="F29" t="n">
-        <v>-151</v>
+        <v>-176</v>
       </c>
       <c r="G29" t="n">
         <v>26</v>
       </c>
       <c r="H29" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -37787,7 +37707,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>左臂J4步进151度，验证超限完整行程150度</t>
+          <t>左臂J4步进176度，验证超出软件行程175度</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -37804,13 +37724,13 @@
         <v>4</v>
       </c>
       <c r="F30" t="n">
-        <v>151</v>
+        <v>176</v>
       </c>
       <c r="G30" t="n">
         <v>35</v>
       </c>
       <c r="H30" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -37824,7 +37744,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>左臂J5步进-328度，验证超限完整行程327度</t>
+          <t>左臂J5步进-332度，验证超出软件行程331度</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -37841,13 +37761,13 @@
         <v>5</v>
       </c>
       <c r="F31" t="n">
-        <v>-328</v>
+        <v>-332</v>
       </c>
       <c r="G31" t="n">
         <v>41</v>
       </c>
       <c r="H31" t="n">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -37861,7 +37781,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>左臂J5步进328度，验证超限完整行程327度</t>
+          <t>左臂J5步进332度，验证超出软件行程331度</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -37878,13 +37798,13 @@
         <v>5</v>
       </c>
       <c r="F32" t="n">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="G32" t="n">
         <v>10</v>
       </c>
       <c r="H32" t="n">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -37898,7 +37818,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>左臂J6步进-130度，验证超限完整行程129度</t>
+          <t>左臂J6步进-122度，验证超出软件行程121度</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -37915,13 +37835,13 @@
         <v>6</v>
       </c>
       <c r="F33" t="n">
-        <v>-130</v>
+        <v>-122</v>
       </c>
       <c r="G33" t="n">
         <v>20</v>
       </c>
       <c r="H33" t="n">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -37935,7 +37855,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>左臂J6步进130度，验证超限完整行程129度</t>
+          <t>左臂J6步进122度，验证超出软件行程121度</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -37952,13 +37872,13 @@
         <v>6</v>
       </c>
       <c r="F34" t="n">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="G34" t="n">
         <v>50</v>
       </c>
       <c r="H34" t="n">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -37972,7 +37892,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>左臂J7步进-173度，验证超限完整行程172度</t>
+          <t>左臂J7步进-157度，验证超出软件行程156度</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -37989,13 +37909,13 @@
         <v>7</v>
       </c>
       <c r="F35" t="n">
-        <v>-173</v>
+        <v>-157</v>
       </c>
       <c r="G35" t="n">
         <v>60</v>
       </c>
       <c r="H35" t="n">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -38009,7 +37929,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>左臂J7步进173度，验证超限完整行程172度</t>
+          <t>左臂J7步进157度，验证超出软件行程156度</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -38026,13 +37946,13 @@
         <v>7</v>
       </c>
       <c r="F36" t="n">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="G36" t="n">
         <v>80</v>
       </c>
       <c r="H36" t="n">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -38046,7 +37966,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>右臂J1步进-327度，验证超限完整行程326度</t>
+          <t>右臂J1步进-328度，验证超出软件行程327度</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -38063,13 +37983,13 @@
         <v>1</v>
       </c>
       <c r="F37" t="n">
-        <v>-327</v>
+        <v>-328</v>
       </c>
       <c r="G37" t="n">
         <v>40</v>
       </c>
       <c r="H37" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -38083,7 +38003,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>右臂J1步进327度，验证超限完整行程326度</t>
+          <t>右臂J1步进328度，验证超出软件行程327度</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -38100,13 +38020,13 @@
         <v>1</v>
       </c>
       <c r="F38" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G38" t="n">
         <v>30</v>
       </c>
       <c r="H38" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -38120,7 +38040,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>右臂J2步进-198度，验证超限完整行程197度</t>
+          <t>右臂J2步进-177度，验证超出软件行程176度</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -38137,13 +38057,13 @@
         <v>2</v>
       </c>
       <c r="F39" t="n">
-        <v>-198</v>
+        <v>-177</v>
       </c>
       <c r="G39" t="n">
         <v>20</v>
       </c>
       <c r="H39" t="n">
-        <v>197</v>
+        <v>176</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -38157,7 +38077,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>右臂J2步进198度，验证超限完整行程197度</t>
+          <t>右臂J2步进177度，验证超出软件行程176度</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -38174,13 +38094,13 @@
         <v>2</v>
       </c>
       <c r="F40" t="n">
-        <v>198</v>
+        <v>177</v>
       </c>
       <c r="G40" t="n">
         <v>10</v>
       </c>
       <c r="H40" t="n">
-        <v>197</v>
+        <v>176</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -38194,7 +38114,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>右臂J3步进-331度，验证超限完整行程330度</t>
+          <t>右臂J3步进-332度，验证超出软件行程331度</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -38211,13 +38131,13 @@
         <v>3</v>
       </c>
       <c r="F41" t="n">
-        <v>-331</v>
+        <v>-332</v>
       </c>
       <c r="G41" t="n">
         <v>20</v>
       </c>
       <c r="H41" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -38231,7 +38151,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>右臂J3步进331度，验证超限完整行程330度</t>
+          <t>右臂J3步进332度，验证超出软件行程331度</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -38248,13 +38168,13 @@
         <v>3</v>
       </c>
       <c r="F42" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G42" t="n">
         <v>49</v>
       </c>
       <c r="H42" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -38268,7 +38188,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>右臂J4步进-151度，验证超限完整行程150度</t>
+          <t>右臂J4步进-176度，验证超出软件行程175度</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -38285,13 +38205,13 @@
         <v>4</v>
       </c>
       <c r="F43" t="n">
-        <v>-151</v>
+        <v>-176</v>
       </c>
       <c r="G43" t="n">
         <v>60</v>
       </c>
       <c r="H43" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -38305,7 +38225,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>右臂J4步进151度，验证超限完整行程150度</t>
+          <t>右臂J4步进176度，验证超出软件行程175度</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -38322,13 +38242,13 @@
         <v>4</v>
       </c>
       <c r="F44" t="n">
-        <v>151</v>
+        <v>176</v>
       </c>
       <c r="G44" t="n">
         <v>80</v>
       </c>
       <c r="H44" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -38342,7 +38262,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>右臂J5步进-328度，验证超限完整行程327度</t>
+          <t>右臂J5步进-332度，验证超出软件行程331度</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -38359,13 +38279,13 @@
         <v>5</v>
       </c>
       <c r="F45" t="n">
-        <v>-328</v>
+        <v>-332</v>
       </c>
       <c r="G45" t="n">
         <v>90</v>
       </c>
       <c r="H45" t="n">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -38379,7 +38299,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>右臂J5步进328度，验证超限完整行程327度</t>
+          <t>右臂J5步进332度，验证超出软件行程331度</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -38396,13 +38316,13 @@
         <v>5</v>
       </c>
       <c r="F46" t="n">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="G46" t="n">
         <v>20</v>
       </c>
       <c r="H46" t="n">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -38416,7 +38336,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>右臂J6步进-130度，验证超限完整行程129度</t>
+          <t>右臂J6步进-122度，验证超出软件行程121度</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -38433,13 +38353,13 @@
         <v>6</v>
       </c>
       <c r="F47" t="n">
-        <v>-130</v>
+        <v>-122</v>
       </c>
       <c r="G47" t="n">
         <v>100</v>
       </c>
       <c r="H47" t="n">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -38453,7 +38373,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>右臂J6步进130度，验证超限完整行程129度</t>
+          <t>右臂J6步进122度，验证超出软件行程121度</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -38470,13 +38390,13 @@
         <v>6</v>
       </c>
       <c r="F48" t="n">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="G48" t="n">
         <v>60</v>
       </c>
       <c r="H48" t="n">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -38490,7 +38410,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>右臂J7步进-173度，验证超限完整行程172度</t>
+          <t>右臂J7步进-157度，验证超出软件行程156度</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -38507,13 +38427,13 @@
         <v>7</v>
       </c>
       <c r="F49" t="n">
-        <v>-173</v>
+        <v>-157</v>
       </c>
       <c r="G49" t="n">
         <v>20</v>
       </c>
       <c r="H49" t="n">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -38527,7 +38447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>右臂J7步进173度，验证超限完整行程172度</t>
+          <t>右臂J7步进157度，验证超出软件行程156度</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -38544,13 +38464,13 @@
         <v>7</v>
       </c>
       <c r="F50" t="n">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="G50" t="n">
         <v>40</v>
       </c>
       <c r="H50" t="n">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -38564,7 +38484,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>双臂J1步进-327度，验证超限完整行程326度</t>
+          <t>双臂J1步进-328度，验证超出软件行程327度</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -38581,13 +38501,13 @@
         <v>1</v>
       </c>
       <c r="F51" t="n">
-        <v>-327</v>
+        <v>-328</v>
       </c>
       <c r="G51" t="n">
         <v>50</v>
       </c>
       <c r="H51" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -38601,7 +38521,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>双臂J1步进327度，验证超限完整行程326度</t>
+          <t>双臂J1步进328度，验证超出软件行程327度</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -38618,13 +38538,13 @@
         <v>1</v>
       </c>
       <c r="F52" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G52" t="n">
         <v>60</v>
       </c>
       <c r="H52" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -38638,7 +38558,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>双臂J2步进-198度，验证超限完整行程197度</t>
+          <t>双臂J2步进-177度，验证超出软件行程176度</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -38655,13 +38575,13 @@
         <v>2</v>
       </c>
       <c r="F53" t="n">
-        <v>-198</v>
+        <v>-177</v>
       </c>
       <c r="G53" t="n">
         <v>70</v>
       </c>
       <c r="H53" t="n">
-        <v>197</v>
+        <v>176</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -38675,7 +38595,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>双臂J2步进198度，验证超限完整行程197度</t>
+          <t>双臂J2步进177度，验证超出软件行程176度</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -38692,13 +38612,13 @@
         <v>2</v>
       </c>
       <c r="F54" t="n">
-        <v>198</v>
+        <v>177</v>
       </c>
       <c r="G54" t="n">
         <v>40</v>
       </c>
       <c r="H54" t="n">
-        <v>197</v>
+        <v>176</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -38712,7 +38632,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>双臂J3步进-331度，验证超限完整行程330度</t>
+          <t>双臂J3步进-332度，验证超出软件行程331度</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -38729,13 +38649,13 @@
         <v>3</v>
       </c>
       <c r="F55" t="n">
-        <v>-331</v>
+        <v>-332</v>
       </c>
       <c r="G55" t="n">
         <v>60</v>
       </c>
       <c r="H55" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -38749,7 +38669,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>双臂J3步进331度，验证超限完整行程330度</t>
+          <t>双臂J3步进332度，验证超出软件行程331度</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -38766,13 +38686,13 @@
         <v>3</v>
       </c>
       <c r="F56" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G56" t="n">
         <v>70</v>
       </c>
       <c r="H56" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -38786,7 +38706,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>双臂J4步进-151度，验证超限完整行程150度</t>
+          <t>双臂J4步进-176度，验证超出软件行程175度</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -38803,13 +38723,13 @@
         <v>4</v>
       </c>
       <c r="F57" t="n">
-        <v>-151</v>
+        <v>-176</v>
       </c>
       <c r="G57" t="n">
         <v>80</v>
       </c>
       <c r="H57" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -38823,7 +38743,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>双臂J4步进151度，验证超限完整行程150度</t>
+          <t>双臂J4步进176度，验证超出软件行程175度</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -38840,13 +38760,13 @@
         <v>4</v>
       </c>
       <c r="F58" t="n">
-        <v>151</v>
+        <v>176</v>
       </c>
       <c r="G58" t="n">
         <v>30</v>
       </c>
       <c r="H58" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -38860,7 +38780,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>双臂J5步进-328度，验证超限完整行程327度</t>
+          <t>双臂J5步进-332度，验证超出软件行程331度</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -38877,13 +38797,13 @@
         <v>5</v>
       </c>
       <c r="F59" t="n">
-        <v>-328</v>
+        <v>-332</v>
       </c>
       <c r="G59" t="n">
         <v>50</v>
       </c>
       <c r="H59" t="n">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -38897,7 +38817,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>双臂J5步进328度，验证超限完整行程327度</t>
+          <t>双臂J5步进332度，验证超出软件行程331度</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -38914,13 +38834,13 @@
         <v>5</v>
       </c>
       <c r="F60" t="n">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="G60" t="n">
         <v>40</v>
       </c>
       <c r="H60" t="n">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -38934,7 +38854,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>双臂J6步进-130度，验证超限完整行程129度</t>
+          <t>双臂J6步进-122度，验证超出软件行程121度</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -38951,13 +38871,13 @@
         <v>6</v>
       </c>
       <c r="F61" t="n">
-        <v>-130</v>
+        <v>-122</v>
       </c>
       <c r="G61" t="n">
         <v>20</v>
       </c>
       <c r="H61" t="n">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -38971,7 +38891,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>双臂J6步进130度，验证超限完整行程129度</t>
+          <t>双臂J6步进122度，验证超出软件行程121度</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -38988,13 +38908,13 @@
         <v>6</v>
       </c>
       <c r="F62" t="n">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="G62" t="n">
         <v>40</v>
       </c>
       <c r="H62" t="n">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -39008,7 +38928,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>双臂J7步进-173度，验证超限完整行程172度</t>
+          <t>双臂J7步进-157度，验证超出软件行程156度</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -39025,13 +38945,13 @@
         <v>7</v>
       </c>
       <c r="F63" t="n">
-        <v>-173</v>
+        <v>-157</v>
       </c>
       <c r="G63" t="n">
         <v>80</v>
       </c>
       <c r="H63" t="n">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -39045,7 +38965,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>双臂J7步进173度，验证超限完整行程172度</t>
+          <t>双臂J7步进157度，验证超出软件行程156度</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -39062,13 +38982,13 @@
         <v>7</v>
       </c>
       <c r="F64" t="n">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="G64" t="n">
         <v>20</v>
       </c>
       <c r="H64" t="n">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -39712,7 +39632,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>左臂J2以速度30执行负向Jog运动到软件限位-72度</t>
+          <t>左臂J2以速度30执行负向Jog运动到软件限位-65度</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -39735,7 +39655,7 @@
         <v>30</v>
       </c>
       <c r="H4" t="n">
-        <v>-72</v>
+        <v>-65</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -39752,7 +39672,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>左臂J2以速度40执行正向Jog运动到软件限位125度</t>
+          <t>左臂J2以速度40执行正向Jog运动到软件限位110度</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -39775,7 +39695,7 @@
         <v>40</v>
       </c>
       <c r="H5" t="n">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -39792,7 +39712,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>左臂J3以速度50执行负向Jog运动到软件限位-163度</t>
+          <t>左臂J3以速度50执行负向Jog运动到软件限位-165度</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -39815,7 +39735,7 @@
         <v>50</v>
       </c>
       <c r="H6" t="n">
-        <v>-163</v>
+        <v>-165</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -39832,7 +39752,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>左臂J3以速度20执行正向Jog运动到软件限位167度</t>
+          <t>左臂J3以速度20执行正向Jog运动到软件限位165度</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -39855,7 +39775,7 @@
         <v>20</v>
       </c>
       <c r="H7" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
@@ -39872,7 +39792,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>左臂J4以速度40执行负向Jog运动到软件限位-149度</t>
+          <t>左臂J4以速度40执行负向Jog运动到软件限位-164度</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -39895,7 +39815,7 @@
         <v>40</v>
       </c>
       <c r="H8" t="n">
-        <v>-149</v>
+        <v>-164</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
@@ -39912,7 +39832,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>左臂J4以速度70执行正向Jog运动到软件限位1度</t>
+          <t>左臂J4以速度70执行正向Jog运动到软件限位-10度</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -39935,7 +39855,7 @@
         <v>70</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>-10</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
@@ -39952,7 +39872,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>左臂J5以速度80执行负向Jog运动到软件限位-179度</t>
+          <t>左臂J5以速度80执行负向Jog运动到软件限位-165度</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -39975,7 +39895,7 @@
         <v>80</v>
       </c>
       <c r="H10" t="n">
-        <v>-179</v>
+        <v>-165</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
@@ -39992,7 +39912,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>左臂J5以速度20执行正向Jog运动到软件限位148度</t>
+          <t>左臂J5以速度20执行正向Jog运动到软件限位165度</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -40015,7 +39935,7 @@
         <v>20</v>
       </c>
       <c r="H11" t="n">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
@@ -40032,7 +39952,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>左臂J6以速度90执行负向Jog运动到软件限位-87度</t>
+          <t>左臂J6以速度90执行负向Jog运动到软件限位-75度</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -40055,7 +39975,7 @@
         <v>90</v>
       </c>
       <c r="H12" t="n">
-        <v>-87</v>
+        <v>-75</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
@@ -40072,7 +39992,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>左臂J6以速度100执行正向Jog运动到软件限位42度</t>
+          <t>左臂J6以速度100执行正向Jog运动到软件限位45度</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -40095,7 +40015,7 @@
         <v>100</v>
       </c>
       <c r="H13" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
@@ -40152,7 +40072,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>左臂J7以速度60执行正向Jog运动到软件限位92度</t>
+          <t>左臂J7以速度60执行正向Jog运动到软件限位75度</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -40175,7 +40095,7 @@
         <v>60</v>
       </c>
       <c r="H15" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
@@ -40272,7 +40192,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>右臂J2以速度10执行负向Jog运动到软件限位-72度</t>
+          <t>右臂J2以速度10执行负向Jog运动到软件限位-65度</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -40295,7 +40215,7 @@
         <v>10</v>
       </c>
       <c r="H18" t="n">
-        <v>-72</v>
+        <v>-65</v>
       </c>
       <c r="I18" t="n">
         <v>1</v>
@@ -40312,7 +40232,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>右臂J2以速度20执行正向Jog运动到软件限位125度</t>
+          <t>右臂J2以速度20执行正向Jog运动到软件限位110度</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -40335,7 +40255,7 @@
         <v>20</v>
       </c>
       <c r="H19" t="n">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="I19" t="n">
         <v>1</v>
@@ -40352,7 +40272,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>右臂J3以速度1执行负向Jog运动到软件限位-163度</t>
+          <t>右臂J3以速度1执行负向Jog运动到软件限位-165度</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -40375,7 +40295,7 @@
         <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>-163</v>
+        <v>-165</v>
       </c>
       <c r="I20" t="n">
         <v>1</v>
@@ -40392,7 +40312,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>右臂J3以速度20执行正向Jog运动到软件限位167度</t>
+          <t>右臂J3以速度20执行正向Jog运动到软件限位165度</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -40415,7 +40335,7 @@
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="I21" t="n">
         <v>1</v>
@@ -40432,7 +40352,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>右臂J4以速度50执行负向Jog运动到软件限位-149度</t>
+          <t>右臂J4以速度50执行负向Jog运动到软件限位-164度</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -40455,7 +40375,7 @@
         <v>50</v>
       </c>
       <c r="H22" t="n">
-        <v>-149</v>
+        <v>-164</v>
       </c>
       <c r="I22" t="n">
         <v>1</v>
@@ -40472,7 +40392,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>右臂J4以速度60执行正向Jog运动到软件限位1度</t>
+          <t>右臂J4以速度60执行正向Jog运动到软件限位-10度</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -40495,7 +40415,7 @@
         <v>60</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>-10</v>
       </c>
       <c r="I23" t="n">
         <v>1</v>
@@ -40512,7 +40432,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>右臂J5以速度80执行负向Jog运动到软件限位-179度</t>
+          <t>右臂J5以速度80执行负向Jog运动到软件限位-165度</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -40535,7 +40455,7 @@
         <v>80</v>
       </c>
       <c r="H24" t="n">
-        <v>-179</v>
+        <v>-165</v>
       </c>
       <c r="I24" t="n">
         <v>1</v>
@@ -40552,7 +40472,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>右臂J5以速度40执行正向Jog运动到软件限位148度</t>
+          <t>右臂J5以速度40执行正向Jog运动到软件限位165度</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -40575,7 +40495,7 @@
         <v>40</v>
       </c>
       <c r="H25" t="n">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="I25" t="n">
         <v>1</v>
@@ -40592,7 +40512,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>右臂J6以速度30执行负向Jog运动到软件限位-87度</t>
+          <t>右臂J6以速度30执行负向Jog运动到软件限位-75度</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -40615,7 +40535,7 @@
         <v>30</v>
       </c>
       <c r="H26" t="n">
-        <v>-87</v>
+        <v>-75</v>
       </c>
       <c r="I26" t="n">
         <v>1</v>
@@ -40632,7 +40552,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>右臂J6以速度20执行正向Jog运动到软件限位42度</t>
+          <t>右臂J6以速度20执行正向Jog运动到软件限位45度</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -40655,7 +40575,7 @@
         <v>20</v>
       </c>
       <c r="H27" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="I27" t="n">
         <v>1</v>
@@ -40712,7 +40632,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>右臂J7以速度26执行正向Jog运动到软件限位92度</t>
+          <t>右臂J7以速度26执行正向Jog运动到软件限位75度</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -40735,7 +40655,7 @@
         <v>26</v>
       </c>
       <c r="H29" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="I29" t="n">
         <v>1</v>
@@ -40832,7 +40752,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>双臂J2以速度10执行负向Jog运动到软件限位-72度</t>
+          <t>双臂J2以速度10执行负向Jog运动到软件限位-65度</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -40855,7 +40775,7 @@
         <v>10</v>
       </c>
       <c r="H32" t="n">
-        <v>-72</v>
+        <v>-65</v>
       </c>
       <c r="I32" t="n">
         <v>1</v>
@@ -40872,7 +40792,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>双臂J3以速度50执行负向Jog运动到软件限位-163度</t>
+          <t>双臂J3以速度50执行负向Jog运动到软件限位-165度</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -40895,7 +40815,7 @@
         <v>50</v>
       </c>
       <c r="H33" t="n">
-        <v>-163</v>
+        <v>-165</v>
       </c>
       <c r="I33" t="n">
         <v>1</v>
@@ -40912,7 +40832,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>双臂J3以速度60执行正向Jog运动到软件限位167度</t>
+          <t>双臂J3以速度60执行正向Jog运动到软件限位165度</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -40935,7 +40855,7 @@
         <v>60</v>
       </c>
       <c r="H34" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="I34" t="n">
         <v>1</v>
@@ -40952,7 +40872,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>双臂J4以速度80执行负向Jog运动到软件限位-149度</t>
+          <t>双臂J4以速度80执行负向Jog运动到软件限位-164度</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -40975,7 +40895,7 @@
         <v>80</v>
       </c>
       <c r="H35" t="n">
-        <v>-149</v>
+        <v>-164</v>
       </c>
       <c r="I35" t="n">
         <v>1</v>
@@ -40992,7 +40912,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>双臂J4以速度40执行正向Jog运动到软件限位1度</t>
+          <t>双臂J4以速度40执行正向Jog运动到软件限位-10度</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -41015,7 +40935,7 @@
         <v>40</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>-10</v>
       </c>
       <c r="I36" t="n">
         <v>1</v>
@@ -41032,7 +40952,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>双臂J5以速度30执行负向Jog运动到软件限位-179度</t>
+          <t>双臂J5以速度30执行负向Jog运动到软件限位-165度</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -41055,7 +40975,7 @@
         <v>30</v>
       </c>
       <c r="H37" t="n">
-        <v>-179</v>
+        <v>-165</v>
       </c>
       <c r="I37" t="n">
         <v>1</v>
@@ -41072,7 +40992,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>双臂J5以速度20执行正向Jog运动到软件限位148度</t>
+          <t>双臂J5以速度20执行正向Jog运动到软件限位165度</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -41095,7 +41015,7 @@
         <v>20</v>
       </c>
       <c r="H38" t="n">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="I38" t="n">
         <v>1</v>
@@ -41112,7 +41032,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>双臂J6以速度10执行负向Jog运动到软件限位-87度</t>
+          <t>双臂J6以速度10执行负向Jog运动到软件限位-75度</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -41135,7 +41055,7 @@
         <v>10</v>
       </c>
       <c r="H39" t="n">
-        <v>-87</v>
+        <v>-75</v>
       </c>
       <c r="I39" t="n">
         <v>1</v>
@@ -41152,7 +41072,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>双臂J6以速度26执行正向Jog运动到软件限位42度</t>
+          <t>双臂J6以速度26执行正向Jog运动到软件限位45度</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -41175,7 +41095,7 @@
         <v>26</v>
       </c>
       <c r="H40" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="I40" t="n">
         <v>1</v>
@@ -41232,7 +41152,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>双臂J7以速度41执行正向Jog运动到软件限位92度</t>
+          <t>双臂J7以速度41执行正向Jog运动到软件限位75度</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -41255,7 +41175,7 @@
         <v>41</v>
       </c>
       <c r="H42" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="I42" t="n">
         <v>1</v>
